--- a/docs/Kubernetesクラスタ_初期構築手順書.xlsx
+++ b/docs/Kubernetesクラスタ_初期構築手順書.xlsx
@@ -20,13 +20,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'作業手順概要'!$A$3:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Phase1_事前準備'!$A$3:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Phase2_OSインストール'!$A$3:$J$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Phase3_OS初期設定'!$A$3:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Phase4_クラスタ構築'!$A$3:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Phase1_事前準備'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Phase2_OSインストール'!$A$3:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Phase3_OS初期設定'!$A$3:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Phase4_クラスタ構築'!$A$3:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase5_ストレージ_GPU設定'!$A$3:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Phase6_監視_RBAC_Namespace設定'!$A$3:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Phase7_バックアップ設定'!$A$3:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Phase6_監視_RBAC_Namespace設定'!$A$3:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Phase7_バックアップ設定'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Phase8_動作確認_完了確認'!$A$3:$J$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,8 +87,13 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +108,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CCECFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -148,16 +158,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,12 +540,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C20"/>
+  <dimension ref="B3:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -588,7 +604,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>第1.0版</t>
+          <t>第1.1版</t>
         </is>
       </c>
     </row>
@@ -629,14 +645,19 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>本書の目的</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>本書の目的・使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="140" customHeight="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>本書は、Kubernetesクラスタ（Vanilla Kubernetes/kubeadm構築、サポート無し・PoC用途）のハードウェア搬入から本番相当の動作確認までの初期構築作業を、実施順に手順化したものである。各作業内容の設定値は「Kubernetesクラスタ_パラメータシート」に記載の値を正とする。「実施結果」欄はプルダウンから選択し、実施者・実施日とあわせて記録すること。「※要決定」の値が残るパラメータは、対応する作業の実施前に確定させること。</t>
+          <t>本書は、Kubernetesクラスタ（Vanilla Kubernetes/kubeadm構築、サポート無し・PoC用途）のハードウェア搬入から動作確認までを、実行するコマンド単位で手順化したものである。原則として、
+・記載順にコマンドを実行することで、Kubernetes基本設計書に記載の設計通りのクラスタが構築できる粒度で記載している。
+・&lt;山括弧&gt;で囲んだ箇所は、パラメータシート「Kubernetesクラスタ_パラメータシート」の確定値に置き換えること。
+・ハードウェア設置・BIOS操作・OSインストーラ操作等、CLIコマンド化できない物理/GUI作業は「作業内容」欄にその旨明記し（オレンジ色セル）、代わりに操作内容と確認コマンドを記載している。
+・バージョン固有のURL/パッケージ名（Calico, Trident, GPU関連等）は本書作成時点（2026年7月）の最新安定版に基づく。実施時点で変更されている場合は、各社の公式リリースページで最新版を確認のうえ読み替えること。
+・「実施結果」欄はプルダウンから選択し、実施者・実施日とあわせて記録すること。</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -644,10 +665,13 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B17:C23"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B17:C20"/>
     <mergeCell ref="B4:C5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -666,13 +690,13 @@
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -741,7 +765,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="27" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -755,14 +779,15 @@
           <t>クラスタ状態最終確認</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>kubectl get nodes -o wide、kubectl get pods -A を実行し、全ノードReady・全PodRunning（Completed含む）であることを確認する。</t>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>kubectl get nodes -o wide
+kubectl get pods -A</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>異常なPod（CrashLoopBackOff等）が無いこと</t>
+          <t>全5ノードがReady、異常なPod(CrashLoopBackOff等)が無いこと</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -790,7 +815,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="39" customHeight="1">
+    <row r="7" ht="432" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
@@ -804,14 +829,42 @@
           <t>サンプルAI学習ジョブ実行</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>GPUリソースを要求するサンプルJobをai-training Namespaceへ投入し、正常完了することを確認する。</t>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF &gt; sample-training-job.yaml
+apiVersion: batch/v1
+kind: Job
+metadata:
+  name: sample-training-job
+  namespace: ai-training
+spec:
+  template:
+    spec:
+      tolerations:
+      - key: nvidia.com/gpu
+        operator: Equal
+        value: present
+        effect: NoSchedule
+      containers:
+      - name: training
+        image: nvidia/cuda:12.6.0-base-ubuntu24.04
+        command: ["nvidia-smi"]
+        resources:
+          requests:
+            cpu: "2"
+            memory: "4Gi"
+          limits:
+            nvidia.com/gpu: 1
+      restartPolicy: Never
+EOF
+kubectl apply -f sample-training-job.yaml
+kubectl wait --for=condition=complete job/sample-training-job -n ai-training --timeout=120s
+kubectl logs job/sample-training-job -n ai-training</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Jobのstatus=Completed、ログにGPU利用が確認できること</t>
+          <t>Job status=Complete、ログにGPU利用（nvidia-smi出力）が確認できること</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -832,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="39" customHeight="1">
+    <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>3</v>
       </c>
@@ -846,14 +899,15 @@
           <t>外部LB経由kube-apiserverアクセス確認</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>controlPlaneEndpoint（VIP:6443）経由でkubectlが利用できることを、cp01以外の経路から確認する。</t>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>curl -k https://&lt;VIP&gt;:6443/healthz
+kubectl --server=https://&lt;VIP&gt;:6443 --insecure-skip-tls-verify get nodes</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>正常にAPIレスポンスが返ること</t>
+          <t>"ok" が返り、正常にノード一覧が取得できること</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -874,7 +928,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
@@ -888,9 +942,12 @@
           <t>NodePort/Service外部アクセス確認</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>検証用ServiceをNodePortで公開し、外部LBのVIP経由でアクセスできることを確認する。</t>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>kubectl expose job/sample-training-job --type=NodePort --port=80 -n ai-training --dry-run=client -o yaml
+# (実運用対象Serviceで)
+kubectl get svc -n &lt;対象namespace&gt;
+curl http://&lt;外部LB VIP&gt;:&lt;NodePort&gt;</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -923,7 +980,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="162" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>5</v>
       </c>
@@ -937,14 +994,23 @@
           <t>Control Plane 1台停止試験</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>任意のControl Plane1台を停止し、クラスタ運用（kubectl操作、既存Pod継続稼働）に影響が無いことを確認する。</t>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t># 対象CPノード上で実行
+sudo systemctl stop kubelet
+sudo systemctl stop containerd
+# 他のCPノードから確認
+kubectl get nodes
+# 業務Podが継続稼働していることを確認
+kubectl get pods -A -o wide
+# 復旧
+sudo systemctl start containerd
+sudo systemctl start kubelet</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>停止中もkubectl操作・既存業務Podが継続動作すること。復電後は自動的にクラスタへ復帰すること</t>
+          <t>停止中もkubectl操作・既存業務Podが継続動作すること。復旧後、対象ノードが自動的にReadyへ復帰すること</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -965,7 +1031,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="39" customHeight="1">
+    <row r="12" ht="148.5" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>6</v>
       </c>
@@ -979,14 +1045,22 @@
           <t>Worker Node 1台停止試験</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Worker1台を停止し、Pod Anti-Affinity設定に基づき残Podが継続稼働することを確認する（GPU学習ジョブは縮退運転となる想定）。</t>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t># 対象Workerノード上で実行
+sudo systemctl stop kubelet
+sudo systemctl stop containerd
+# cp01から確認
+kubectl get nodes
+kubectl get pods -A -o wide
+# 復旧
+sudo systemctl start containerd
+sudo systemctl start kubelet</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>正常ノードで業務継続、GPU学習ジョブは順次実行に切り替わること</t>
+          <t>正常ノードで業務継続、GPU学習ジョブは縮退運転（順次実行）に切り替わること。復旧後、自動的にReadyへ復帰すること</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -1014,7 +1088,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="39" customHeight="1">
+    <row r="14" ht="40.5" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>7</v>
       </c>
@@ -1028,14 +1102,15 @@
           <t>サービス一覧・パッケージ一覧採取</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>systemctl list-unit-files、dpkg -l の結果を採取し、パラメータシート「構築後採取一覧」へ転記する。</t>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>systemctl list-unit-files &gt; service-list-$(hostname).txt
+dpkg -l &gt; package-list-$(hostname).txt</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>採取結果がパラメータシートへ反映されていること</t>
+          <t>各ノードでファイルが生成され、内容がパラメータシート「構築後採取一覧」へ転記されていること</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -1056,7 +1131,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>8</v>
       </c>
@@ -1070,14 +1145,16 @@
           <t>クラスタ情報・Helmリリース一覧採取</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>kubectl get nodes -o wide、kubectl version、helm list -A の結果を採取し、パラメータシート「構築後採取一覧」へ転記する。</t>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>kubectl get nodes -o wide &gt; cluster-nodes.txt
+kubectl version &gt; cluster-version.txt
+helm list -A &gt; helm-releases.txt</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>採取結果がパラメータシートへ反映されていること</t>
+          <t>各ファイルが生成され、内容がパラメータシート「構築後採取一覧」へ転記されていること</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -1098,7 +1175,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>9</v>
       </c>
@@ -1112,9 +1189,10 @@
           <t>完了報告・サインオフ</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>全フェーズの実施結果を確認し、関係者による完了確認・承認を行う。</t>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>（レビュー・承認作業のためCLIコマンド無し）
+本手順書全項目の実施結果を確認し、関係者による完了確認・承認を行う。</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -1168,8 +1246,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
@@ -1274,7 +1352,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="39" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
@@ -1285,7 +1363,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Kubernetes前提のOS設定（swap無効化、sysctl、containerd等）</t>
+          <t>Kubernetes前提のOS設定（swap無効化、sysctl、containerd、kubeadm等の導入）</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1469,19 +1547,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1550,7 +1628,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -1564,19 +1642,20 @@
           <t>ラック搭載・電源結線</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Control Plane×3（HPE DL360 Gen12）、Worker×2（HPE DL380 Gen12）をラックへ搭載し、電源ケーブル（冗長電源2系統）を結線する。</t>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>（物理作業のためCLIコマンド無し）
+Control Plane×3（HPE DL360 Gen12）、Worker×2（HPE DL380 Gen12）をラックへ搭載し、冗長電源2系統を結線する。ノード用NIC・iLO用NICを、パラメータシート「ノード構成」記載のスイッチポートへ結線する。</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>両電源ユニットのランプ点灯を目視確認</t>
+          <t>両電源ユニットのランプ点灯、スイッチ側のリンクアップランプ点灯を目視確認</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート ハードウェア設定</t>
+          <t>パラメータシート ノード構成、ハードウェア設定</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -1588,11 +1667,11 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>搬入時の外観・型番も併せて確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
+          <t>CLIコマンド無し（現地物理作業のため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
@@ -1603,22 +1682,26 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>ネットワークケーブル結線</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>ノード用NIC・iLO用NICを、パラメータシート「ノード構成」記載のスイッチポートへ結線する。</t>
+          <t>iLO(BMC)初期設定・疎通確認</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t># 管理端末から疎通確認
+ping -c 4 &lt;各ノードのiLO IPアドレス&gt;
+# ブラウザで https://&lt;iLOのIPアドレス&gt;/ にアクセスしログイン
+# (初回パスワードは筐体銘板のiLOデフォルトパスワードラベルを参照)
+# ログイン後、管理者パスワードを変更する</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>スイッチ側でリンクアップを確認</t>
+          <t>ping応答成功、Web GUIへのログイン成功</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート ノード構成</t>
+          <t>ハードウェア設定 サーバ管理モジュール</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -1630,11 +1713,11 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
+          <t>変更後のパスワードは本書に記載せず、パスワード管理台帳で管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
@@ -1645,22 +1728,26 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>iLO(BMC)初期設定・疎通確認</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>各ノードiLOへ初期IPアドレスを設定し、管理端末からpingおよびWeb GUIログインを確認する。</t>
+          <t>BIOS設定確認</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>（BIOSメニュー操作のためCLIコマンド無し）
+起動時にF9等でBIOSセットアップへ入り、以下を設定する。
+- Virtualization Technology (VT-x/VT-d): Enabled
+- Boot Mode: UEFI
+- Power Profile: Maximum Performance</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>iLO Web GUIへのログイン成功</t>
+          <t>BIOS設定画面で各項目が設定値通りであることを目視確認</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>ハードウェア設定 サーバ管理モジュール</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1672,11 +1759,11 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>出荷時パスワードは初回ログイン後に変更</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1">
+          <t>CLIコマンド無し（BIOSメニュー操作のため）。iLO RESTful API（iLOREST）による自動化も可能（本書では対象外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
@@ -1687,22 +1774,24 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>BIOS設定確認</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>仮想化支援機能（Intel VT-x/VT-d）有効化、UEFIブートモード、電源管理をHigh Performanceに設定する。</t>
+          <t>RAID構成確認</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t># HPE Smart Storage Administrator CLI(ssacli)で論理ドライブを確認（Ubuntu起動後に実施）
+sudo apt-get install -y ssacli
+sudo ssacli ctrl slot=0 ld all show detail</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>BIOS設定画面で各項目が設定値通りであることを確認</t>
+          <t>Bootドライブ論理ドライブ=RAID1、Worker用データSSD論理ドライブ=RAID10、いずれもStatus=OKであること</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>パラメータシート ハードウェア設定</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -1714,60 +1803,66 @@
       <c r="I8" s="11" t="inlineStr"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="11" t="n">
+          <t>ssacliパッケージはHPE公式リポジトリから導入</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>【外部インタフェース準備】</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="81" customHeight="1">
+      <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>全5ノード</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>RAID構成確認</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Bootドライブ=RAID1、Worker用データSSD=RAID10で構成されていることをiLO/RAIDコントローラ管理画面で確認する。</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>論理ドライブのRAIDレベルと状態(Optimal)を確認</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート ハードウェア設定</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>【外部インタフェース準備】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>外部LB</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>kube-apiserver用VIP設定</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>（ベンダー製品のGUI/CLI操作のため個別コマンド無し）
+外部ロードバランサ管理画面で以下を設定する。
+- VIP: &lt;controlPlaneEndpoint用VIP&gt;
+- リスナーポート: TCP/6443
+- バックエンド: k8s-cp01/02/03 の 6443番ポート
+- ヘルスチェック: TCP/6443（この時点ではAPIサーバー未構築のため疎通のみ）</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t># 管理端末から経路疎通確認（未構築のため6443でRST/timeoutでも経路上の疎通確認としては可）
+nc -zv &lt;VIP&gt; 6443</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>基本設計書3.5.5、パラメータシート ノード構成</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>ベンダー製品固有の設定コマンドは外部LB設計書に準ずる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
@@ -1778,22 +1873,23 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>kube-apiserver用VIP設定</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>外部ロードバランサにControlPlaneEndpoint用VIP（TCP/6443）を設定し、バックエンドにCP×3を登録する。ヘルスチェックはTCP/6443疎通を基本とする。</t>
+          <t>NodePort公開用VIP設定</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>（ベンダー製品のGUI/CLI操作）
+業務アプリケーション公開用VIPを設定し、バックエンドにWorker×2のNodePortレンジ(30000-32767)を登録する。</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>VIPへのTCP/6443疎通確認（この時点ではCP未構築のためRST/timeoutでも可、経路疎通のみ確認）</t>
+          <t>設定内容のレビュー完了、nc -zv &lt;VIP&gt; &lt;確認用ポート&gt; で経路疎通確認</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>基本設計書3.5.5、パラメータシート ノード構成</t>
+          <t>基本設計書3.5.5</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1805,37 +1901,40 @@
       <c r="I11" s="11" t="inlineStr"/>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>詳細ヘルスチェック方式は外部LB設計書に準ずる</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39" customHeight="1">
+          <t>公開対象Serviceが未確定の場合は仮設定とし、Phase8で実サービスに合わせて調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>外部LB</t>
+          <t>DNS/NTPサーバー</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>NodePort公開用VIP設定</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>業務アプリケーション公開用のVIPを設定し、バックエンドにWorker×2のNodePortレンジを登録する。</t>
+          <t>DNS正引き・逆引き登録</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>（DNS管理コンソール/ゾーンファイル編集のため個別コマンド無し）
+全5ノードのAレコード・PTRレコードを登録する。</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>設定内容のレビュー完了</t>
+          <t>dig k8s-cp01.&lt;ドメイン名&gt;
+dig -x &lt;k8s-cp01のIPアドレス&gt;
+（他4ノードも同様に確認）</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>基本設計書3.5.5</t>
+          <t>基本設計書3.5.2</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -1847,11 +1946,11 @@
       <c r="I12" s="11" t="inlineStr"/>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>公開対象Serviceが未確定の場合は仮設定とし後日調整</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39" customHeight="1">
+          <t>DNS製品固有の登録手順（BIND/Windows DNS等）は別途参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40.5" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
@@ -1862,22 +1961,24 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>DNS正引き・逆引き登録</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>全5ノードのホスト名とIPアドレスをDNSサーバーへ登録する。</t>
+          <t>NTPサーバー疎通確認</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t># 確認用に一時導入し疎通確認（恒常設定はPhase3で実施）
+sudo apt-get install -y ntpdate
+ntpdate -q &lt;NTPサーバーのIPアドレス&gt;</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>各ノードから nslookup / dig で正引き・逆引きが解決できること</t>
+          <t>オフセット値が返り疎通できること</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>基本設計書3.5.2</t>
+          <t>基本設計書3.5.1</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1889,37 +1990,43 @@
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39" customHeight="1">
+          <t>恒常的な時刻同期はPhase3のchrony設定で実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="94.5" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>DNS/NTPサーバー</t>
+          <t>全5ノード</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>NTPサーバー疎通確認</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート記載のNTPサーバーへ、各ノード予定IPからUDP/123疎通が可能なことを確認する。</t>
+          <t>外部リポジトリ疎通確認</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>curl -I https://registry.k8s.io
+curl -I https://pkgs.k8s.io
+curl -I https://download.docker.com
+curl -I https://hub.docker.com
+curl -I https://archive.ubuntu.com
+curl -I https://netapp.github.io
+curl -I https://nvidia.github.io</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>ntpdate等での時刻取得成功、または管理端末からの疎通確認</t>
+          <t>各URLで200または30x応答が返ること（プロキシ経由の場合は各コマンドへ -x &lt;proxyURL&gt; を付与）</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>基本設計書3.5.1</t>
+          <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -1931,111 +2038,70 @@
       <c r="I14" s="11" t="inlineStr"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="11" t="n">
+          <t>疎通不可の場合は社内プロキシ設定をOS設定へ追記</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>【最終値確定】</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
+      <c r="A16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>全5ノード</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>外部リポジトリ疎通確認</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Docker Hub、registry.k8s.io、pkgs.k8s.io、Ubuntuパッケージリポジトリへの疎通を確認する（プロキシ経由の場合はプロキシ設定を含む）。</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>各ノード予定セグメントからcurl等で200応答を確認</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート OS設定_共通 導入パッケージ</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>社内プロキシ経由が必要な場合はOS設定へプロキシ設定を追記</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>【最終値確定】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>全5ノード</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>IPアドレス・ホスト名の最終確定</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>各ノードのIPアドレス、controlPlaneEndpoint、podSubnet等「※要決定」項目を確定し、パラメータシートへ反映する。</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>（設計判断作業のためCLIコマンド無し）
+パラメータシート「ノード構成」シートの各ノードIPアドレス、controlPlaneEndpoint、podSubnet等の「※要決定」項目を確定し反映する。</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>パラメータシートの「※要決定」項目がすべて確定値に更新されていること</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>パラメータシート 全シート</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr"/>
+      <c r="I16" s="11" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>確定後、後続フェーズの前提となるため関係者レビューを実施</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J17"/>
+  <autoFilter ref="A3:J16"/>
   <mergeCells count="4">
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G11 G12 G13 G14 G15 G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G10 G11 G12 G13 G14 G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2049,19 +2115,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2130,7 +2196,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="39" customHeight="1">
+    <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -2144,9 +2210,10 @@
           <t>インストールメディア準備</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Ubuntu Server 24.04 LTS ISOイメージをiLO仮想メディア機能等で各ノードにマウントする。</t>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>（物理/iLO仮想メディア操作のためCLIコマンド無し）
+Ubuntu Server 24.04 LTS ISOイメージをiLO仮想メディア機能等で各ノードにマウントする。</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -2168,18 +2235,18 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>CLIコマンド無し（iLO GUI操作のため）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>【インストーラでの設定（全ノード共通）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
+          <t>【インストーラでの設定（全ノード共通・手動インストールの場合）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
@@ -2190,12 +2257,13 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>言語・タイムゾーン設定</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>言語=English、タイムゾーン=Asia/Tokyo、キーボード=Japaneseを選択する。</t>
+          <t>言語・地域設定</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>（インストーラGUI/TUI操作のためCLIコマンド無し）
+言語=English、タイムゾーン=Asia/Tokyo、キーボード=Japaneseを選択する。</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2217,11 +2285,11 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1">
+          <t>CLIコマンド無し（対話式インストーラのため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>3</v>
       </c>
@@ -2235,14 +2303,15 @@
           <t>ネットワーク設定</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>IPv4手動設定でパラメータシート記載のIPアドレス・ネットマスク・ゲートウェイ・DNSを入力し、ホスト名を設定する。IPv6は無効化する。</t>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>（インストーラGUI/TUI操作）
+IPv4手動設定でパラメータシート記載のIPアドレス・ネットマスク・ゲートウェイ・DNSを入力し、ホスト名を設定する。IPv6は無効化する。</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>インストーラのネットワークテスト、または再起動後のip addr確認</t>
+          <t>インストーラのネットワークテスト成功、または再起動後 ip a / hostnamectl で確認</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -2259,11 +2328,11 @@
       <c r="I8" s="11" t="inlineStr"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="39" customHeight="1">
+          <t>CLIコマンド無し（対話式インストーラのため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
@@ -2277,14 +2346,15 @@
           <t>ディスクパーティション設定</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>手動構成を選択し、/（ext4）、/boot/efi（EFI System Partition）を作成する。swap領域は作成しない。</t>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>（インストーラGUI/TUI操作）
+手動構成を選択し、/（ext4）、/boot/efi（EFI System Partition, 600MB）を作成する。swap領域は作成しない。</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>lsblk / df -h でパーティション構成を確認</t>
+          <t>再起動後 lsblk / df -h でパーティション構成を確認</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -2301,11 +2371,11 @@
       <c r="I9" s="11" t="inlineStr"/>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>swap未作成であることを必ず確認（kubelet起動要件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="39" customHeight="1">
+          <t>swap未作成であることを必ず確認（kubelet起動要件）。CLIコマンド無し（対話式インストーラのため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
@@ -2319,9 +2389,10 @@
           <t>管理ユーザー作成</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>管理ユーザーを作成し、SSH公開鍵を登録する。rootの直接ログインは無効のままとする。</t>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>（インストーラGUI/TUI操作）
+管理ユーザーを作成し、SSH公開鍵を登録する。rootの直接ログインは無効のままとする。</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -2343,61 +2414,152 @@
       <c r="I10" s="11" t="inlineStr"/>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>パスワードは本手順書・パラメータシートに記載せず、パスワード管理台帳で管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="11" t="n">
+          <t>パスワードは本書・パラメータシートに記載せず、パスワード管理台帳で管理。CLIコマンド無し（対話式インストーラのため）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>【自動インストール(autoinstall)を用いる場合（任意・複数台展開時に推奨）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="432" customHeight="1">
+      <c r="A12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>全5ノード</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>インストール実行・初回起動確認</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>インストールを実行し、再起動後にSSHで疎通確認する。</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>管理端末からSSHログイン成功、uname -a でカーネルバージョン確認</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>autoinstall用user-data作成</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>#cloud-config形式のuser-dataを作成し、USBメディア等に配置する（ノードごとにIP/ホスト名を変更）
+autoinstall:
+  version: 1
+  locale: en_US.UTF-8
+  keyboard:
+    layout: jp
+  network:
+    version: 2
+    ethernets:
+      eth0:
+        addresses: [&lt;ノードのIPアドレス&gt;/24]
+        gateway4: &lt;ゲートウェイ&gt;
+        nameservers:
+          addresses: [&lt;DNSサーバー&gt;]
+  storage:
+    layout:
+      name: direct
+  identity:
+    hostname: &lt;ホスト名&gt;
+    username: &lt;管理ユーザー名&gt;
+    password: "&lt;mkpasswd -m sha-512 で生成したハッシュ&gt;"
+  ssh:
+    install-server: true
+    authorized-keys:
+      - "&lt;管理端末のSSH公開鍵&gt;"
+  late-commands:
+    - "curtin in-target -- swapoff -a"
+    - "sed -i '/\\sswap\\s/d' /target/etc/fstab"</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>（本手順を使う場合）自動インストール完了後、Phase2最終確認へ進む</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>パラメータシート OS設定_共通</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>swapを作らないlate-commandsを明示している点がKubernetes向けの固有設定。手動インストールを行う場合は本行は対象外とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>【インストール完了後の確認（全ノード共通）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="94.5" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>全5ノード</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>初回起動・疎通確認</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t># 管理端末から実行
+ssh &lt;管理ユーザー&gt;@&lt;ノードのIPアドレス&gt;
+ip a
+hostnamectl
+df -h
+free -h
+uname -a</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>SSHログイン成功、IPアドレス・ホスト名・パーティション構成が設計値通りであること、free -h でSwap行が0であること</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>パラメータシート ノード構成、OS設定_共通</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="11" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J11"/>
-  <mergeCells count="3">
+  <autoFilter ref="A3:J14"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G7 G8 G9 G10 G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G7 G8 G9 G10 G12 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2411,19 +2573,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2492,7 +2654,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="27" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -2506,9 +2668,10 @@
           <t>OSパッケージ更新</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>apt update &amp;&amp; apt upgrade -y を実行する。</t>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>sudo apt-get update
+sudo apt-get upgrade -y</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -2534,7 +2697,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="39" customHeight="1">
+    <row r="6" ht="27" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
@@ -2545,17 +2708,18 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>ファイアーウォール(ufw)無効化確認</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>ufw status がinactiveであることを確認する（Kubernetes/CNIが管理するiptablesとの競合回避）。</t>
+          <t>ファイアーウォール(ufw)無効化</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>sudo systemctl disable --now ufw
+sudo ufw status</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>ufw status → inactive</t>
+          <t>"Status: inactive" と表示されること</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -2572,11 +2736,11 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>本番移行時は再検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
+          <t>Kubernetes/CNIが管理するiptablesとの競合回避のため</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="108" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
@@ -2590,14 +2754,21 @@
           <t>chrony設定</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>/etc/chrony/chrony.conf にパラメータシート記載のNTPサーバーを設定し、systemctl enable --now chronyを実行する。</t>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>sudo apt-get install -y chrony
+sudo tee -a /etc/chrony/chrony.conf &gt; /dev/null &lt;&lt;EOF
+server &lt;NTPサーバー1&gt; iburst
+server &lt;NTPサーバー2&gt; iburst
+EOF
+sudo systemctl enable --now chrony
+sudo systemctl restart chrony</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>chronyc sources で同期先が表示され、chronyc tracking でLeap statusがNormalであること</t>
+          <t>chronyc sources で同期先が表示されること
+chronyc tracking で Leap status: Normal であること</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -2618,7 +2789,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="148.5" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
@@ -2632,14 +2803,21 @@
           <t>unattended-upgrades設定</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>/etc/apt/apt.conf.d/50unattended-upgrades でsecurityのみ有効化し、自動再起動を無効化する。</t>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>sudo apt-get install -y unattended-upgrades
+sudo tee /etc/apt/apt.conf.d/50unattended-upgrades &gt; /dev/null &lt;&lt;EOF
+Unattended-Upgrade::Allowed-Origins {
+    "\${distro_id}:\${distro_codename}-security";
+};
+Unattended-Upgrade::Automatic-Reboot "false";
+EOF
+sudo systemctl enable --now unattended-upgrades</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>unattended-upgrade --dry-run --debug でsecurity対象のみ検出されること</t>
+          <t>sudo unattended-upgrade --dry-run --debug でsecurity対象のみ検出されること</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -2656,7 +2834,7 @@
       <c r="I8" s="11" t="inlineStr"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Kubernetes関連パッケージは対象外（apt-mark holdで別途固定）</t>
+          <t>Kubernetes関連パッケージはapt-mark holdで別途固定するため対象外となる</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2845,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="39" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
@@ -2681,14 +2859,16 @@
           <t>swap無効化</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>swapoff -a を実行し、/etc/fstab のswap行を削除またはコメントアウトする。</t>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>sudo swapoff -a
+sudo sed -i.bak '/\sswap\s/s/^/#/' /etc/fstab
+free -h</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>free -h でSwap行が0であること。再起動後も無効のままであること</t>
+          <t>free -h の Swap 行が 0 であること。再起動後も無効のままであること</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -2709,7 +2889,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="94.5" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
@@ -2723,14 +2903,19 @@
           <t>カーネルモジュール設定</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>/etc/modules-load.d/k8s.conf に overlay と br_netfilter を記載し、modprobeで即時ロードする。</t>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF | sudo tee /etc/modules-load.d/k8s.conf
+overlay
+br_netfilter
+EOF
+sudo modprobe overlay
+sudo modprobe br_netfilter</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>lsmod | grep -e overlay -e br_netfilter でロード済みを確認</t>
+          <t>lsmod | grep -e overlay -e br_netfilter でいずれもロード済みであること</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -2751,7 +2936,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="78" customHeight="1">
+    <row r="12" ht="81" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>7</v>
       </c>
@@ -2765,14 +2950,19 @@
           <t>sysctl設定</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>/etc/sysctl.d/k8s.conf に net.bridge.bridge-nf-call-iptables=1、net.bridge.bridge-nf-call-ip6tables=1、net.ipv4.ip_forward=1 を設定し、sysctl --systemを実行する。</t>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF | sudo tee /etc/sysctl.d/k8s.conf
+net.bridge.bridge-nf-call-iptables  = 1
+net.bridge.bridge-nf-call-ip6tables = 1
+net.ipv4.ip_forward                 = 1
+EOF
+sudo sysctl --system</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>sysctl &lt;各パラメータ&gt; で設定値が反映されていることを確認</t>
+          <t>sysctl net.ipv4.ip_forward 等、各パラメータが設定値通りであること</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -2796,11 +2986,11 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>【コンテナランタイム・Kubernetesパッケージ導入（全5ノード共通）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
+          <t>【コンテナランタイム導入（全5ノード共通）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="202.5" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>8</v>
       </c>
@@ -2814,14 +3004,21 @@
           <t>containerdインストール</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>containerd 2.3.x をインストールし、/etc/containerd/config.toml にSystemdCgroup=true、sandbox image、レジストリミラー設定を反映する。</t>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t># Docker公式aptリポジトリからcontainerd.ioパッケージを導入（Ubuntu 24.04標準リポジトリより新しいバージョンを利用するため）
+sudo install -m 0755 -d /etc/apt/keyrings
+curl -fsSL https://download.docker.com/linux/ubuntu/gpg -o /etc/apt/keyrings/docker.asc
+sudo chmod a+r /etc/apt/keyrings/docker.asc
+echo "deb [arch=$(dpkg --print-architecture) signed-by=/etc/apt/keyrings/docker.asc] https://download.docker.com/linux/ubuntu $(. /etc/os-release &amp;&amp; echo \"$VERSION_CODENAME\") stable" | sudo tee /etc/apt/sources.list.d/docker.list &gt; /dev/null
+sudo apt-get update
+sudo apt-get install -y containerd.io
+ctr version</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>systemctl status containerd がactiveであること、ctr version でバージョン確認</t>
+          <t>ctr version の出力バージョンが2.3系であること</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -2842,7 +3039,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="91" customHeight="1">
+    <row r="15" ht="135" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>9</v>
       </c>
@@ -2853,22 +3050,28 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>kubeadm/kubelet/kubectlインストール</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>pkgs.k8s.ioリポジトリを登録し、v1.35.x系のkubeadm/kubelet/kubectlをインストールしてapt-mark holdでバージョン固定する。</t>
+          <t>containerd設定反映</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>sudo mkdir -p /etc/containerd
+containerd config default | sudo tee /etc/containerd/config.toml &gt; /dev/null
+sudo sed -i 's/SystemdCgroup = false/SystemdCgroup = true/' /etc/containerd/config.toml
+sudo sed -i 's#sandbox_image = .*#sandbox_image = "registry.k8s.io/pause:3.10"#' /etc/containerd/config.toml
+sudo systemctl restart containerd
+sudo systemctl enable containerd</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>kubeadm version / kubelet --version / kubectl version --client でバージョン確認、apt-mark showholdで固定確認</t>
+          <t>grep SystemdCgroup /etc/containerd/config.toml → true であること
+systemctl status containerd がactiveであること</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート Kubernetes設定、OS設定_共通</t>
+          <t>パラメータシート Kubernetes設定 containerd設定</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -2880,86 +3083,98 @@
       <c r="I15" s="11" t="inlineStr"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="11" t="n">
+          <t>SystemdCgroup=trueはkubelet(systemdドライバ)との整合に必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>【kubeadm/kubelet/kubectl導入（全5ノード共通）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="202.5" customHeight="1">
+      <c r="A17" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Control Planeのみ</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Helmインストール</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Helm v4.2.x をインストールする（監視スタック等のデプロイに使用）。</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>helm version でバージョン確認</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート OS設定_共通</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>v3系Chart利用時は互換性を事前確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>【GPU関連（Worker Nodeのみ）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>全5ノード</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Kubernetes aptリポジトリ登録・パッケージ導入</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>sudo apt-get install -y apt-transport-https ca-certificates curl gpg
+sudo mkdir -p /etc/apt/keyrings
+curl -fsSL https://pkgs.k8s.io/core:/stable:/v1.35/deb/Release.key | sudo gpg --dearmor -o /etc/apt/keyrings/kubernetes-apt-keyring.gpg
+echo 'deb [signed-by=/etc/apt/keyrings/kubernetes-apt-keyring.gpg] https://pkgs.k8s.io/core:/stable:/v1.35/deb/ /' | sudo tee /etc/apt/sources.list.d/kubernetes.list
+sudo apt-get update
+sudo apt-get install -y kubelet kubeadm kubectl
+sudo apt-mark hold kubelet kubeadm kubectl
+kubeadm version</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>kubeadm version / kubelet --version / kubectl version --client でv1.35系が表示されること
+apt-mark showhold で3パッケージが固定されていること</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>パラメータシート Kubernetes設定、OS設定_共通</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>v1.35リポジトリ内の最新パッチが自動選択される（構築時点でv1.32はEOLのため使用しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="81" customHeight="1">
       <c r="A18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Worker×2</t>
+          <t>Control Planeのみ(cp01-03)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>NVIDIA Driver / Container Toolkitインストール</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>構築時最新の推奨版のNVIDIA DriverおよびNVIDIA Container Toolkitをインストールし、containerdのGPUランタイム設定を反映する。</t>
+          <t>Helmインストール</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>curl -fsSL -o helm.tar.gz https://get.helm.sh/helm-v4.2.3-linux-amd64.tar.gz
+tar -zxvf helm.tar.gz
+sudo mv linux-amd64/helm /usr/local/bin/helm
+rm -rf helm.tar.gz linux-amd64
+helm version</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>nvidia-smi でGPU認識・ドライババージョンを確認</t>
+          <t>helm version の出力が v4.2.3 系であること</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>基本設計書3.8、パラメータシート Kubernetes設定</t>
+          <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -2971,86 +3186,95 @@
       <c r="I18" s="11" t="inlineStr"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
+          <t>既存Chart/CIがv3系前提の場合は互換性を事前確認。実施時点の最新版は https://github.com/helm/helm/releases で要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>【GPU関連（Worker Nodeのみ: wk01, wk02）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="67.5" customHeight="1">
+      <c r="A20" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Worker×2</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>NVIDIA Driverインストール</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>sudo apt-get install -y ubuntu-drivers-common
+sudo ubuntu-drivers install --gpgpu
+sudo reboot
+# 再起動後
+nvidia-smi</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>nvidia-smi でH100 NVLが認識され、ドライババージョンが表示されること</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>基本設計書3.8、パラメータシート Kubernetes設定</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Worker×2</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>nfs-commonインストール</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>NetApp Trident（NFSバックエンド）利用の前提としてnfs-commonパッケージを導入する。</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>dpkg -l | grep nfs-common で導入確認</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート Kubernetes設定 CSI設定</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>【再起動・最終確認】</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="91" customHeight="1">
+    <row r="21" ht="216" customHeight="1">
       <c r="A21" s="11" t="n">
         <v>13</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>全5ノード</t>
+          <t>Worker×2</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>再起動・状態確認</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>各ノードを再起動し、swap無効・sysctl設定・containerd/kubelet未起動（未クラスタ参加のため）の状態を確認する。</t>
+          <t>NVIDIA Container Toolkitインストール</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>curl -fsSL https://nvidia.github.io/libnvidia-container/gpgkey | sudo gpg --dearmor -o /usr/share/keyrings/nvidia-container-toolkit-keyring.gpg
+curl -s -L https://nvidia.github.io/libnvidia-container/stable/deb/nvidia-container-toolkit.list | sed 's#deb https://#deb [signed-by=/usr/share/keyrings/nvidia-container-toolkit-keyring.gpg] https://#g' | sudo tee /etc/apt/sources.list.d/nvidia-container-toolkit.list
+sudo apt-get update
+sudo apt-get install -y nvidia-container-toolkit
+sudo nvidia-ctk runtime configure --runtime=containerd
+sudo systemctl restart containerd</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>free -h、systemctl status containerd がactive、kubelet はクラスタ未参加のためactivating(auto-restart)で正常</t>
+          <t>nvidia-ctk --version でバージョン確認、grep nvidia /etc/containerd/config.toml でruntime設定が反映されていること</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>基本設計書3.8、パラメータシート Kubernetes設定</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -3066,18 +3290,114 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Worker×2</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>nfs-commonインストール</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>sudo apt-get install -y nfs-common</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>dpkg -l | grep nfs-common で導入確認</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>パラメータシート Kubernetes設定 CSI設定</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="11" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>NetApp Trident（NFSバックエンド）利用の前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>【最終確認】</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="67.5" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>全5ノード</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>再起動・状態確認</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>sudo reboot
+# 再起動後
+free -h
+systemctl status containerd
+systemctl status kubelet</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Swap=0、containerdがactive、kubeletはクラスタ未参加のためactivating(auto-restart)で正常であること</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr"/>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J21"/>
-  <mergeCells count="6">
+  <autoFilter ref="A3:J24"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A16:J16"/>
     <mergeCell ref="A13:J13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G10 G11 G12 G14 G15 G16 G18 G19 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G10 G11 G12 G14 G15 G17 G18 G20 G21 G22 G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3091,19 +3411,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3168,11 +3488,11 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>【Control Plane初期構築】</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
+          <t>【Control Plane初期構築（k8s-cp01）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="391.5" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -3183,17 +3503,42 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>kubeadm init実行</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>kubeadm init --control-plane-endpoint "&lt;VIP&gt;:6443" --pod-network-cidr=192.168.0.0/16 --upload-certs --kubernetes-version v1.35.x を実行する。</t>
+          <t>kubeadm-config.yaml作成</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t># kubeadm versionでインストール済みバージョンを確認
+kubeadm version -o short
+# 上記バージョンを反映してkubeadm-config.yamlを作成
+cat &lt;&lt;EOF &gt; kubeadm-config.yaml
+apiVersion: kubeadm.k8s.io/v1beta4
+kind: ClusterConfiguration
+kubernetesVersion: "&lt;kubeadm versionで確認したバージョン&gt;"
+clusterName: kubernetes
+controlPlaneEndpoint: "&lt;VIP&gt;:6443"
+networking:
+  podSubnet: 192.168.0.0/16
+  serviceSubnet: 10.96.0.0/12
+  dnsDomain: cluster.local
+etcd:
+  local:
+    dataDir: /var/lib/etcd
+---
+apiVersion: kubeadm.k8s.io/v1beta4
+kind: InitConfiguration
+nodeRegistration:
+  criSocket: unix:///var/run/containerd/containerd.sock
+---
+apiVersion: kubelet.config.k8s.io/v1beta1
+kind: KubeletConfiguration
+cgroupDriver: systemd
+EOF</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>コマンドが正常終了し、join用コマンド（Control Plane用/Worker用）が出力されること</t>
+          <t>ファイル内容がパラメータシート「Kubernetes設定 kubeadm ClusterConfiguration」の値と一致していること</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -3210,11 +3555,11 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>出力されるjoinコマンド・certificate-keyを安全に控える（有効期限あり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
+          <t>apiVersion(v1beta4)は本書作成時点の最新。実施時に異なる場合は kubeadm config migrate で変換可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="67.5" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
@@ -3225,17 +3570,17 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>kubectl設定</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>$HOME/.kube/config に admin.conf を配置する。</t>
+          <t>kubeadm init実行</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>sudo kubeadm init --config kubeadm-config.yaml --upload-certs | tee kubeadm-init.log</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>kubectl get nodes が実行できること（この時点ではcp01のみNotReady表示）</t>
+          <t>"Your Kubernetes control-plane has initialized successfully" が出力され、Control Plane用joinコマンド・Worker用joinコマンドが出力されること</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -3252,32 +3597,35 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>CNI未導入のためNotReadyが正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+          <t>出力されたjoinコマンド・certificate-keyをkubeadm-init.logごと安全に保管する（certificate-keyの既定有効期限は2時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>k8s-cp02, cp03</t>
+          <t>k8s-cp01</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Control Plane追加join</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>kubeadm init出力のControl Plane用joinコマンド（--control-plane --certificate-key含む）をcp02・cp03で実行する。</t>
+          <t>kubectl設定</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>mkdir -p $HOME/.kube
+sudo cp -i /etc/kubernetes/admin.conf $HOME/.kube/config
+sudo chown $(id -u):$(id -g) $HOME/.kube/config
+kubectl get nodes</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>各ノードでコマンドが正常終了すること</t>
+          <t>kubectl get nodes が実行でき、k8s-cp01のみSTATUS=NotReadyで表示されること（CNI未導入のため正常）</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -3294,60 +3642,66 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>certificate-keyの有効期限(既定2時間)に注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1">
-      <c r="A8" s="11" t="n">
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>【Control Plane追加（k8s-cp02, cp03）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="175.5" customHeight="1">
+      <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>k8s-cp01</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Control Plane 3台の参加確認</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>kubectl get nodes でcp01～03が表示されることを確認する（CNI未導入のためNotReady）。</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>3ノードすべてが一覧に表示されること</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>基本設計書4.1.1</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>k8s-cp02, cp03</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Control Plane追加join</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t># kubeadm-init.logに出力された、以下形式のControl Plane用joinコマンドを実行する
+sudo kubeadm join &lt;VIP&gt;:6443 --token &lt;token&gt; \
+  --discovery-token-ca-cert-hash sha256:&lt;hash&gt; \
+  --control-plane --certificate-key &lt;certificate-key&gt;
+mkdir -p $HOME/.kube
+sudo cp -i /etc/kubernetes/admin.conf $HOME/.kube/config
+sudo chown $(id -u):$(id -g) $HOME/.kube/config</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>各ノードで "This node has joined the cluster" 相当のメッセージが出力されること</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>【CNI（Calico）導入】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr"/>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>token(既定24時間)・certificate-key(既定2時間)が期限切れの場合は次行の再発行コマンドを使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
@@ -3358,22 +3712,23 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Tigera Operatorインストール</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Tigera Operatorのmanifestを適用する。</t>
+          <t>(期限切れ時のみ)token/certificate-key再発行</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>sudo kubeadm init phase upload-certs --upload-certs
+sudo kubeadm token create --print-join-command</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>kubectl get pods -n tigera-operator でPodがRunningになること</t>
+          <t>新しいtoken/certificate-keyが出力されること</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート Kubernetes設定 CNI設定</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -3385,11 +3740,11 @@
       <c r="I10" s="11" t="inlineStr"/>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
+          <t>期限切れが無ければ本行はスキップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40.5" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
@@ -3400,22 +3755,22 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Calico custom-resources適用</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>IPPool CIDR=192.168.0.0/16、カプセル化方式、blockSize=/26、natOutgoing有効をcustom-resources.yamlへ反映し適用する。</t>
+          <t>Control Plane 3台の参加確認</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>kubectl get nodes</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>kubectl get pods -n calico-system で全PodがRunningになること</t>
+          <t>cp01, cp02, cp03の3ノードが表示されること（CNI未導入のため全てNotReady）</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート Kubernetes設定 CNI設定</t>
+          <t>基本設計書4.1.1</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -3427,86 +3782,108 @@
       <c r="I11" s="11" t="inlineStr"/>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>カプセル化方式は入門コース確認結果を反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="11" t="n">
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>【CNI（Calico v3.32.x）導入】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="94.5" customHeight="1">
+      <c r="A13" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>k8s-cp01</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Control Plane Ready確認</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>kubectl get nodes でcp01～03がReadyになることを確認する。</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>3ノードすべてがSTATUS=Readyであること</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>【Worker Node参加】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Calico CRD・Tigera Operatorインストール</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>kubectl create -f https://raw.githubusercontent.com/projectcalico/calico/v3.32.1/manifests/v1_crd_projectcalico_org.yaml
+kubectl create -f https://raw.githubusercontent.com/projectcalico/calico/v3.32.1/manifests/tigera-operator.yaml
+kubectl get pods -n tigera-operator</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>tigera-operator NamespaceのPodがRunningになること</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>パラメータシート Kubernetes設定 CNI設定</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr"/>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>サイズが大きいためkubectl applyではなくkubectl createを使用する（公式手順）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="297" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>k8s-wk01, wk02</t>
+          <t>k8s-cp01</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Worker join実行</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>kubeadm init出力のWorker用joinコマンドをwk01・wk02で実行する。</t>
+          <t>Calico custom-resources適用</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF &gt; custom-resources.yaml
+apiVersion: operator.tigera.io/v1
+kind: Installation
+metadata:
+  name: default
+spec:
+  calicoNetwork:
+    ipPools:
+    - name: default-ipv4-ippool
+      cidr: 192.168.0.0/16
+      encapsulation: &lt;VXLANCrossSubnet等・要決定値を反映&gt;
+      natOutgoing: Enabled
+      blockSize: 26
+---
+apiVersion: operator.tigera.io/v1
+kind: APIServer
+metadata:
+  name: default
+spec: {}
+EOF
+kubectl create -f custom-resources.yaml</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>各ノードでコマンドが正常終了すること</t>
+          <t>kubectl get pods -n calico-system で全PodがRunningになること（数分要する）</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>パラメータシート Kubernetes設定 CNI設定</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -3518,11 +3895,11 @@
       <c r="I14" s="11" t="inlineStr"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>tokenの有効期限(既定24時間)に注意。期限切れ時はkubeadm token createで再発行</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
+          <t>カプセル化方式(encapsulation)は入門コースでの確認結果を反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>9</v>
       </c>
@@ -3533,17 +3910,17 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>全ノードReady確認</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>kubectl get nodes -o wide で全5ノードがReadyであることを確認する。</t>
+          <t>Control Plane Ready確認</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>kubectl get nodes</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>5ノードすべてがSTATUS=Readyであること</t>
+          <t>cp01, cp02, cp03の3ノードすべてがSTATUS=Readyであること</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -3564,75 +3941,42 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="11" t="n">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>【Worker Node参加】</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>k8s-cp01</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Control Plane taint確認</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>kubectl describe node &lt;cp名&gt; でnode-role.kubernetes.io/control-plane:NoScheduleのtaintが付与されていることを確認する（kubeadmにより自動付与）。</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Taints欄に該当taintが表示されること</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート Kubernetes設定 Pod配置・リソース管理</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>k8s-wk01, wk02</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Worker join実行</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t># kubeadm-init.logに出力された、以下形式のWorker用joinコマンドを実行する
+sudo kubeadm join &lt;VIP&gt;:6443 --token &lt;token&gt; \
+  --discovery-token-ca-cert-hash sha256:&lt;hash&gt;</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>各ノードで "This node has joined the cluster" が出力されること</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>k8s-cp01</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>クラスタ証明書有効期限確認</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>kubeadm certs check-expiration を実行し、各証明書の有効期限を記録する。</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>コマンドが正常実行され、期限一覧が出力されること</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>基本設計書4.4.2</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -3644,20 +3988,149 @@
       <c r="I17" s="11" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
+          <t>tokenが期限切れの場合はcp01で kubeadm token create --print-join-command</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>k8s-cp01</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>全ノードReady確認</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>kubectl get nodes -o wide</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>全5ノードがSTATUS=Readyであること</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
+      <c r="I18" s="11" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="81" customHeight="1">
+      <c r="A19" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>k8s-cp01</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Control Plane taint確認</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>kubectl describe node k8s-cp01 | grep -A3 Taints
+kubectl describe node k8s-cp02 | grep -A3 Taints
+kubectl describe node k8s-cp03 | grep -A3 Taints</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>各CPノードに node-role.kubernetes.io/control-plane:NoSchedule のtaintが表示されること（kubeadmにより自動付与）</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>パラメータシート Kubernetes設定 Pod配置・リソース管理</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>k8s-cp01</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>クラスタ証明書有効期限確認</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>sudo kubeadm certs check-expiration</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>コマンドが正常実行され、各証明書の有効期限一覧が出力されること</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>基本設計書4.4.2</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
           <t>証明書監視の初期値として記録</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J17"/>
-  <mergeCells count="4">
+  <autoFilter ref="A3:J20"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G10 G11 G12 G14 G15 G16 G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G6 G7 G9 G10 G11 G13 G14 G15 G17 G18 G19 G20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3677,13 +4150,13 @@
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3748,11 +4221,11 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>【CSI（NetApp Trident）導入】</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
+          <t>【CSI（NetApp Trident v26.06）導入】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -3766,19 +4239,20 @@
           <t>ONTAP側接続情報確認</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>管理LIF疎通、利用予定SVM・アグリゲート・プロトコル(NFS)の準備状況を外部ストレージ管理者と確認する。</t>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>（外部ストレージ管理者との調整作業のためCLIコマンド無し）
+管理LIF疎通、利用予定SVM・アグリゲート・プロトコル(NFS)の準備状況を確認する。</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>管理LIFへの疎通確認、SVM/アグリゲートの空き容量確認</t>
+          <t>ping &lt;ONTAP管理LIFのIPアドレス&gt; で疎通確認。SVM/アグリゲートの空き容量確認</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>基本設計書3.7.2（※接続情報は未パラメータ化のため別途確定）</t>
+          <t>基本設計書3.7.2（※接続情報は未パラメータ化のため本行で確定）</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -3790,11 +4264,11 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>TridentBackend定義に必要な値をここで確定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
+          <t>TridentBackendConfig作成に必要な値をここで確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="108" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
@@ -3808,14 +4282,18 @@
           <t>Trident Operatorインストール</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>helmまたはtridentctlでTrident（v26.06）をtrident Namespaceへインストールする。</t>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>kubectl create namespace trident
+helm repo add netapp-trident https://netapp.github.io/trident-helm-chart
+helm repo update
+helm install trident netapp-trident/trident-operator --version 100.2606.0 --namespace trident
+kubectl get pods -n trident</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>kubectl get pods -n trident でPodがRunningになること</t>
+          <t>trident Namespace配下のPod(trident-operator, trident-controller等)がRunningになること</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -3832,11 +4310,11 @@
       <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+          <t>Helm Chartバージョン100.2606.0がTrident 26.06に対応（実施時は要最新確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="67.5" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
@@ -3847,17 +4325,20 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>TridentBackend作成</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>確定した接続情報（管理LIF/SVM/アグリゲート/プロトコル）でTridentBackendリソースを作成する。</t>
+          <t>ONTAP接続用Secret作成</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>kubectl create secret generic backend-tbc-ontap-nas-secret \
+  --from-literal=username=&lt;ONTAP接続ユーザー名&gt; \
+  --from-literal=password=&lt;ONTAP接続パスワード&gt; \
+  -n trident</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>kubectl get tridentbackendconfig でPhase=Boundとなること</t>
+          <t>kubectl get secret -n trident でSecretが作成されていること</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -3874,11 +4355,11 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
+          <t>認証情報は本書・パラメータシートに記載せず、パスワード管理台帳で管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="216" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
@@ -3889,22 +4370,37 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>StorageClass作成</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>reclaimPolicy=Delete、volumeBindingMode=Immediate、allowVolumeExpansion=trueでStorageClassを作成し、デフォルトStorageClassに指定する。</t>
+          <t>TridentBackendConfig作成</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF &gt; backend-ontap-nas.yaml
+apiVersion: trident.netapp.io/v1
+kind: TridentBackendConfig
+metadata:
+  name: backend-ontap-nas
+  namespace: trident
+spec:
+  version: 1
+  storageDriverName: ontap-nas
+  managementLIF: &lt;ONTAP管理LIFのIPアドレス&gt;
+  dataLIF: &lt;ONTAPデータLIFのIPアドレス&gt;
+  svm: &lt;SVM名&gt;
+  credentials:
+    name: backend-tbc-ontap-nas-secret
+EOF
+kubectl apply -f backend-ontap-nas.yaml</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>kubectl get storageclass で作成済み・(default)表示を確認</t>
+          <t>kubectl get tridentbackendconfig -n trident で Phase=Bound であること</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート Kubernetes設定 CSI設定</t>
+          <t>基本設計書3.7.2</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -3920,7 +4416,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="39" customHeight="1">
+    <row r="9" ht="229.5" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
@@ -3931,22 +4427,37 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>PVC/Pod動作確認</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>検証用PVCとPodを作成し、ファイルの書き込み・読み込みができることを確認する。</t>
+          <t>StorageClass作成</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF &gt; storageclass-netapp-nas.yaml
+apiVersion: storage.k8s.io/v1
+kind: StorageClass
+metadata:
+  name: netapp-nas
+  annotations:
+    storageclass.kubernetes.io/is-default-class: "true"
+provisioner: csi.trident.netapp.io
+parameters:
+  backendType: "ontap-nas"
+  storagePools: "backend-ontap-nas:.*"
+reclaimPolicy: Delete
+volumeBindingMode: Immediate
+allowVolumeExpansion: true
+EOF
+kubectl apply -f storageclass-netapp-nas.yaml</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pod内でのファイル書き込み・再作成後の読み込みに成功すること</t>
+          <t>kubectl get storageclass で netapp-nas が (default) 付きで表示されること</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>パラメータシート Kubernetes設定 CSI設定</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -3958,86 +4469,121 @@
       <c r="I9" s="11" t="inlineStr"/>
       <c r="J9" s="12" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="472.5" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>k8s-cp01</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>PVC/Pod動作確認</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF &gt; test-pvc-pod.yaml
+apiVersion: v1
+kind: PersistentVolumeClaim
+metadata:
+  name: test-pvc
+spec:
+  accessModes: ["ReadWriteOnce"]
+  storageClassName: netapp-nas
+  resources:
+    requests:
+      storage: 1Gi
+---
+apiVersion: v1
+kind: Pod
+metadata:
+  name: test-pod
+spec:
+  containers:
+  - name: test
+    image: busybox
+    command: ["sh", "-c", "echo hello &gt; /data/test.txt &amp;&amp; sleep 3600"]
+    volumeMounts:
+    - name: vol
+      mountPath: /data
+  volumes:
+  - name: vol
+    persistentVolumeClaim:
+      claimName: test-pvc
+EOF
+kubectl apply -f test-pvc-pod.yaml
+kubectl wait --for=condition=Ready pod/test-pod --timeout=120s
+kubectl exec test-pod -- cat /data/test.txt
+kubectl delete -f test-pvc-pod.yaml</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>"hello" が出力されること（PV経由での書き込み・読み込み成功）</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
           <t>確認後、検証用リソースは削除する</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>【GPU設定（Worker Nodeのみ）】</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>k8s-wk01, wk02</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>NVIDIA Device Pluginデプロイ</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>NVIDIA Device PluginをDaemonSetとしてデプロイする。</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>kubectl get pods -n kube-system -l name=nvidia-device-plugin-ds でRunningを確認</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>パラメータシート Kubernetes設定 GPU設定</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>GPU Operator採用の場合は代替手順とする</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39" customHeight="1">
+    <row r="12" ht="94.5" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>k8s-wk01, wk02</t>
+          <t>k8s-cp01</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>GPUノードtaint付与</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>kubectl taint nodes &lt;wk名&gt; nvidia.com/gpu=present:NoSchedule を実行する。</t>
+          <t>NVIDIA Device Pluginデプロイ</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>helm repo add nvdp https://nvidia.github.io/k8s-device-plugin
+helm repo update
+helm upgrade -i nvdp nvdp/nvidia-device-plugin \
+  --namespace nvidia-device-plugin --create-namespace --version 0.17.1</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>kubectl describe node でTaintsに反映されていることを確認</t>
+          <t>kubectl get pods -n nvidia-device-plugin でRunningを確認</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート Kubernetes設定 GPU設定、Pod配置・リソース管理</t>
+          <t>パラメータシート Kubernetes設定 GPU設定</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -4049,11 +4595,11 @@
       <c r="I12" s="11" t="inlineStr"/>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
+          <t>GPU Operator採用の場合は代替手順とする（本手順はDevice Plugin単体導入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
@@ -4064,22 +4610,23 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>GPU認識確認</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>kubectl describe node &lt;wk名&gt; の Capacity/Allocatable に nvidia.com/gpu: 1 が表示されることを確認する。</t>
+          <t>GPUノードtaint付与</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>kubectl taint nodes k8s-wk01 nvidia.com/gpu=present:NoSchedule
+kubectl taint nodes k8s-wk02 nvidia.com/gpu=present:NoSchedule</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>nvidia.com/gpuリソースが表示されること</t>
+          <t>kubectl describe node k8s-wk01 | grep Taints で反映を確認</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>パラメータシート Kubernetes設定 GPU設定、Pod配置・リソース管理</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -4095,7 +4642,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="39" customHeight="1">
+    <row r="14" ht="378" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>9</v>
       </c>
@@ -4106,17 +4653,41 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>GPU動作確認Pod実行</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>toleration付きの検証Podでnvidia-smiを実行し、GPUが認識されることを確認する。</t>
+          <t>GPU認識・動作確認</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>kubectl describe node k8s-wk01 | grep -A5 Capacity
+cat &lt;&lt;EOF &gt; gpu-test.yaml
+apiVersion: v1
+kind: Pod
+metadata:
+  name: gpu-test
+spec:
+  tolerations:
+  - key: nvidia.com/gpu
+    operator: Equal
+    value: present
+    effect: NoSchedule
+  containers:
+  - name: cuda
+    image: nvidia/cuda:12.6.0-base-ubuntu24.04
+    command: ["nvidia-smi"]
+    resources:
+      limits:
+        nvidia.com/gpu: 1
+  restartPolicy: Never
+EOF
+kubectl apply -f gpu-test.yaml
+kubectl wait --for=condition=Ready pod/gpu-test --timeout=60s || true
+kubectl logs gpu-test
+kubectl delete -f gpu-test.yaml</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Pod内nvidia-smi出力にH100 NVLが表示されること</t>
+          <t>Capacity欄に nvidia.com/gpu: 1 が表示され、Pod実行ログにH100 NVLの情報が出力されること</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -4142,10 +4713,10 @@
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G11 G12 G13 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4159,19 +4730,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4240,7 +4811,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="39" customHeight="1">
+    <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -4254,9 +4825,11 @@
           <t>Namespace作成</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>monitoring、ai-training、analyticsの各Namespaceを作成する。</t>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>kubectl create namespace monitoring
+kubectl create namespace ai-training
+kubectl create namespace analytics</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -4289,7 +4862,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
@@ -4303,14 +4876,14 @@
           <t>Kubernetes管理者権限設定</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>管理者用ユーザー/グループにcluster-admin（ClusterRoleBinding）を付与する。</t>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>kubectl create clusterrolebinding k8s-admins --clusterrole=cluster-admin --user=&lt;管理者ユーザー&gt;</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>kubectl auth can-i "*" "*" --as=&lt;管理者&gt; がyesとなること</t>
+          <t>kubectl auth can-i "*" "*" --as=&lt;管理者ユーザー&gt; が yes となること</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -4327,11 +4900,11 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>cluster-admin付与は管理者のみに限定</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
+          <t>cluster-admin付与はKubernetes管理者のみに限定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="162" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>3</v>
       </c>
@@ -4345,9 +4918,13 @@
           <t>運用担当者/アプリ利用者権限設定</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Namespace単位のRole/RoleBindingで運用担当者（admin相当）、アプリ利用者（view）を設定する。</t>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t># Namespace単位で組み込みClusterRole(admin/view)をRoleBindingとして割り当てる
+kubectl create rolebinding ai-training-admin --clusterrole=admin --user=&lt;運用担当者&gt; -n ai-training
+kubectl create rolebinding ai-training-viewer --clusterrole=view --user=&lt;アプリ利用者&gt; -n ai-training
+kubectl create rolebinding analytics-admin --clusterrole=admin --user=&lt;運用担当者&gt; -n analytics
+kubectl create rolebinding analytics-viewer --clusterrole=view --user=&lt;アプリ利用者&gt; -n analytics</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -4373,7 +4950,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="78" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
@@ -4387,14 +4964,16 @@
           <t>監視用ServiceAccount作成</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>monitoring Namespaceに閲覧権限(view相当)のServiceAccountを作成する。</t>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>kubectl create serviceaccount monitoring-viewer -n monitoring
+kubectl create clusterrolebinding monitoring-viewer-binding \
+  --clusterrole=view --serviceaccount=monitoring:monitoring-viewer</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>kubectl auth can-i get pods --as=system:serviceaccount:monitoring:&lt;sa名&gt; -A がyesであること</t>
+          <t>kubectl auth can-i get pods --as=system:serviceaccount:monitoring:monitoring-viewer -A が yes であること</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -4418,11 +4997,11 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>【監視スタック導入】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
+          <t>【監視スタック導入（kube-prometheus-stack）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="310.5" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>5</v>
       </c>
@@ -4433,17 +5012,39 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>kube-prometheus-stack導入</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Helm Chartリポジトリを登録し、values.yamlに保存期間・PVサイズ・Alertmanager通知先を反映してmonitoring Namespaceへインストールする。</t>
+          <t>values-monitoring.yaml作成</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF &gt; values-monitoring.yaml
+prometheus:
+  prometheusSpec:
+    retention: 15d
+    storageSpec:
+      volumeClaimTemplate:
+        spec:
+          storageClassName: netapp-nas
+          accessModes: ["ReadWriteOnce"]
+          resources:
+            requests:
+              storage: 100Gi
+alertmanager:
+  config:
+    route:
+      receiver: "email-notifications"
+    receivers:
+    - name: "email-notifications"
+      email_configs:
+      - to: "&lt;通知先メールアドレス&gt;"
+        from: "&lt;送信元メールアドレス&gt;"
+        smarthost: "&lt;SMTPサーバー&gt;:25"
+EOF</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>kubectl get pods -n monitoring で全PodがRunningになること</t>
+          <t>ファイル内容がパラメータシート「Kubernetes設定 監視設定」の値と一致していること</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -4464,7 +5065,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="39" customHeight="1">
+    <row r="12" ht="108" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>6</v>
       </c>
@@ -4475,22 +5076,26 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>DCGM Exporter導入</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Worker Node限定（nodeSelector/toleration設定）でDCGM ExporterをデプロイしGPUメトリクスを収集する。</t>
+          <t>kube-prometheus-stackインストール</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>helm repo add prometheus-community https://prometheus-community.github.io/helm-charts
+helm repo update
+helm install monitoring prometheus-community/kube-prometheus-stack \
+  --namespace monitoring --values values-monitoring.yaml
+kubectl get pods -n monitoring</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Prometheus targetsでDCGM Exporterがupと表示されること</t>
+          <t>monitoring Namespace配下の全Pod(Prometheus/Alertmanager/Grafana/各Exporter)がRunningになること</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>パラメータシート Kubernetes設定 監視設定</t>
+          <t>基本設計書4.4.1</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -4506,33 +5111,40 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="148.5" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>確認端末</t>
+          <t>k8s-cp01</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Grafanaダッシュボード疎通確認</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>GrafanaへログインしKubernetes標準ダッシュボードが表示されることを確認する。</t>
+          <t>DCGM Exporter導入（GPUメトリクス）</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>helm repo add gpu-helm-charts https://nvidia.github.io/gpu-monitoring-tools/helm-charts
+helm repo update
+helm install dcgm-exporter gpu-helm-charts/dcgm-exporter --namespace monitoring \
+  --set nodeSelector."nvidia\.com/gpu\.present"=true \
+  --set tolerations[0].key=nvidia.com/gpu \
+  --set tolerations[0].operator=Equal \
+  --set tolerations[0].value=present \
+  --set tolerations[0].effect=NoSchedule</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>ノード/Podメトリクスがグラフ表示されること</t>
+          <t>kubectl get pods -n monitoring -l app.kubernetes.io/name=dcgm-exporter でGPU搭載Worker上にのみPodがRunningであること</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>基本設計書4.4.1</t>
+          <t>パラメータシート Kubernetes設定 監視設定</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -4544,11 +5156,11 @@
       <c r="I13" s="11" t="inlineStr"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>初期パスワードは変更しパスワード管理台帳で管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="94.5" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>8</v>
       </c>
@@ -4559,22 +5171,24 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Alertmanagerテスト通知確認</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>疑似的にアラートを発火させ、設定した通知先にメールが届くことを確認する。</t>
+          <t>Grafanaダッシュボード疎通確認</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>kubectl get secret monitoring-grafana -n monitoring -o jsonpath="{.data.admin-password}" | base64 -d; echo
+kubectl port-forward -n monitoring svc/monitoring-grafana 3000:80
+# ブラウザで http://localhost:3000 へアクセスし、上記adminパスワードでログイン</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>テスト通知メールの受信を確認</t>
+          <t>ログイン成功、Kubernetes標準ダッシュボードでノード/Podメトリクスが表示されること</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>基本設計書4.4.3</t>
+          <t>基本設計書4.4.1</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -4586,12 +5200,55 @@
       <c r="I14" s="11" t="inlineStr"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>確認後、テスト用アラートルールは削除・無効化する</t>
+          <t>初期パスワードはログイン後に変更し、パスワード管理台帳で管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="81" customHeight="1">
+      <c r="A15" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>確認端末</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Alertmanagerテスト通知確認</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>kubectl port-forward -n monitoring svc/monitoring-kube-prometheus-alertmanager 9093:9093 &amp;
+curl -H "Content-Type: application/json" -d '[{"labels":{"alertname":"TestAlert","severity":"critical"}}]' http://localhost:9093/api/v2/alerts</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>設定した通知先へテスト通知メールが届くこと</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>基本設計書4.4.3</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>確認後、テスト用アラートは自動的にresolvedとなり通知される</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J14"/>
+  <autoFilter ref="A3:J15"/>
   <mergeCells count="4">
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A1:J1"/>
@@ -4599,7 +5256,7 @@
     <mergeCell ref="A10:J10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G7 G8 G9 G11 G12 G13 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G7 G8 G9 G11 G12 G13 G14 G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4613,19 +5270,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4694,7 +5351,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="39" customHeight="1">
+    <row r="5" ht="189" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -4705,17 +5362,28 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>etcdスナップショット取得設定</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>etcdctl snapshot save を毎日00:00に実行するcronまたはsystemdタイマーを各Control Planeに設定する。</t>
+          <t>etcdスナップショット取得スクリプト作成</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>sudo mkdir -p /var/backups/etcd
+cat &lt;&lt;EOF | sudo tee /usr/local/bin/etcd-snapshot.sh
+#!/bin/bash
+set -e
+ETCDCTL_API=3 etcdctl snapshot save /var/backups/etcd/snapshot-\$(date +%Y%m%d).db \
+  --endpoints=https://127.0.0.1:2379 \
+  --cacert=/etc/kubernetes/pki/etcd/ca.crt \
+  --cert=/etc/kubernetes/pki/etcd/server.crt \
+  --key=/etc/kubernetes/pki/etcd/server.key
+find /var/backups/etcd -mtime +7 -delete
+EOF
+sudo chmod +x /usr/local/bin/etcd-snapshot.sh</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>設定したジョブが有効化されていること（systemctl list-timers等）</t>
+          <t>ファイルが作成され実行権限が付与されていること</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -4732,32 +5400,49 @@
       <c r="I5" s="11" t="inlineStr"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>保管先・世代数は運用ルールとして別途確定</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
+          <t>保管世代数(7日)は運用ルールに応じて調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="351" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>k8s-cp01</t>
+          <t>k8s-cp01～03</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>スナップショット初回取得確認</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>初回のetcdスナップショットが正常に取得できることを確認する。</t>
+          <t>systemdタイマー設定（毎日00:00実行）</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>cat &lt;&lt;EOF | sudo tee /etc/systemd/system/etcd-snapshot.service
+[Unit]
+Description=etcd snapshot backup
+[Service]
+Type=oneshot
+ExecStart=/usr/local/bin/etcd-snapshot.sh
+EOF
+cat &lt;&lt;EOF | sudo tee /etc/systemd/system/etcd-snapshot.timer
+[Unit]
+Description=Daily etcd snapshot at 00:00
+[Timer]
+OnCalendar=*-*-* 00:00:00
+Persistent=true
+[Install]
+WantedBy=timers.target
+EOF
+sudo systemctl daemon-reload
+sudo systemctl enable --now etcd-snapshot.timer</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>スナップショットファイルの生成、etcdutl snapshot statusでの整合性確認</t>
+          <t>systemctl list-timers | grep etcd-snapshot でタイマーが登録され次回実行時刻が表示されること</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -4778,7 +5463,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="39" customHeight="1">
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
@@ -4789,22 +5474,24 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>リストア手順の検証</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>検証用環境または別クラスタで、取得したスナップショットからのリストア手順を一度実施し、手順の妥当性を確認する。</t>
+          <t>スナップショット初回取得確認</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>sudo /usr/local/bin/etcd-snapshot.sh
+ls -la /var/backups/etcd/
+sudo ETCDCTL_API=3 etcdutl snapshot status /var/backups/etcd/snapshot-*.db -w table</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>リストア後にkubectl get nodes等でクラスタ状態が復元されること</t>
+          <t>スナップショットファイルが生成され、snapshot statusでhash/revision等が正常表示されること</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>基本設計書4.2.2</t>
+          <t>基本設計書4.2.1</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -4816,68 +5503,114 @@
       <c r="I7" s="11" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>本番相当環境が無い場合は手順書レビューのみでも可（要合意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="67.5" customHeight="1">
+      <c r="A8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>検証環境</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>リストア手順の検証</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t># 検証用に別ディレクトリへリストア（本番データには影響しない）
+sudo ETCDCTL_API=3 etcdutl snapshot restore /var/backups/etcd/snapshot-&lt;日付&gt;.db \
+  --data-dir /var/lib/etcd-restore-test
+ls /var/lib/etcd-restore-test</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>エラー無くリストアが完了し、データディレクトリが生成されること</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>基本設計書4.2.2</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="11" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>本番環境への切替(mv /var/lib/etcd 等)はクラスタ全損時のみ実施する非常時手順のため、平常時は検証のみ実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>【OSバックアップ】</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>全5ノード</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>外部バックアップソフトウェア設定</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>外部バックアップソフトウェアによる毎日00:00の定期バックアップ設定を全ノードへ実施する。</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>初回バックアップジョブが正常終了すること</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>（バックアップ製品固有のGUI/CLI操作のため個別コマンド無し）
+外部バックアップソフトウェアによる毎日00:00の定期バックアップジョブを全ノードへ設定する。</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>初回バックアップジョブが正常終了すること（バックアップ管理コンソールで確認）</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.2.1</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>バックアップ製品名確定後に本行を更新</t>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>バックアップ製品名・具体的な設定コマンドは製品確定後に本行を更新</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J9"/>
+  <autoFilter ref="A3:J10"/>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/Kubernetesクラスタ_初期構築手順書.xlsx
+++ b/docs/Kubernetesクラスタ_初期構築手順書.xlsx
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'作業手順概要'!$A$3:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Phase1_事前準備'!$A$3:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Phase2_OSインストール'!$A$3:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Phase3_OS初期設定'!$A$3:$J$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Phase4_クラスタ構築'!$A$3:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase5_ストレージ_GPU設定'!$A$3:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Phase6_監視_RBAC_Namespace設定'!$A$3:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Phase7_バックアップ設定'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Phase8_動作確認_完了確認'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Phase1_事前準備'!$A$3:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Phase2_OSインストール'!$A$3:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Phase3_OS初期設定'!$A$3:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Phase4_クラスタ構築'!$A$3:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Phase5_ストレージ_GPU設定'!$A$3:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Phase6_監視_RBAC_Namespace設定'!$A$3:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Phase7_バックアップ設定'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Phase8_動作確認_完了確認'!$A$3:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,7 +93,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +108,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CCECFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F9F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,7 +174,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -540,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C23"/>
+  <dimension ref="B3:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -604,7 +612,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>第1.1版</t>
+          <t>第1.2版</t>
         </is>
       </c>
     </row>
@@ -649,10 +657,11 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="140" customHeight="1">
+    <row r="17" ht="160" customHeight="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>本書は、Kubernetesクラスタ（Vanilla Kubernetes/kubeadm構築、サポート無し・PoC用途）のハードウェア搬入から動作確認までを、実行するコマンド単位で手順化したものである。原則として、
+          <t>本書は、Kubernetesクラスタ（Vanilla Kubernetes/kubeadm構築、サポート無し・PoC用途）のハードウェア搬入から動作確認までを、実行するコマンド単位で手順化したものである。
+・「目的・解説」欄（緑色セル）には、その作業がなぜ必要か（設計上の理由・やらないとどうなるか）を記載している。単なる作業のなぞりではなく、意味を理解した上で実施・レビューできることを意図している。
 ・記載順にコマンドを実行することで、Kubernetes基本設計書に記載の設計通りのクラスタが構築できる粒度で記載している。
 ・&lt;山括弧&gt;で囲んだ箇所は、パラメータシート「Kubernetesクラスタ_パラメータシート」の確定値に置き換えること。
 ・ハードウェア設置・BIOS操作・OSインストーラ操作等、CLIコマンド化できない物理/GUI作業は「作業内容」欄にその旨明記し（オレンジ色セル）、代わりに操作内容と確認コマンドを記載している。
@@ -668,10 +677,11 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
+    <row r="24"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B17:C23"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B17:C24"/>
     <mergeCell ref="B4:C5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -684,19 +694,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -724,35 +735,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -765,7 +781,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1">
+    <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -779,30 +795,35 @@
           <t>クラスタ状態最終確認</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>個別フェーズでは正常に見えても、全体を通して異常なPodや未Ready状態のノードが残っていないかを、最終的に俯瞰で確認するため。</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>kubectl get nodes -o wide
 kubectl get pods -A</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>全5ノードがReady、異常なPod(CrashLoopBackOff等)が無いこと</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -829,7 +850,12 @@
           <t>サンプルAI学習ジョブ実行</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>本クラスタの目的であるAI学習ワークロードが、設計通りGPUを利用して実際に動作することを確認する、最も重要な受け入れ試験。</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF &gt; sample-training-job.yaml
 apiVersion: batch/v1
@@ -862,24 +888,24 @@
 kubectl logs job/sample-training-job -n ai-training</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Job status=Complete、ログにGPU利用（nvidia-smi出力）が確認できること</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 Pod配置・リソース管理</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -899,30 +925,35 @@
           <t>外部LB経由kube-apiserverアクセス確認</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>実際の運用ではControl Plane個別ノードのIPではなく外部LBのVIP経由でアクセスする（基本設計書3.5.5）ため、設計通りの経路で本当に到達できるかを確認する必要がある。</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>curl -k https://&lt;VIP&gt;:6443/healthz
 kubectl --server=https://&lt;VIP&gt;:6443 --insecure-skip-tls-verify get nodes</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>"ok" が返り、正常にノード一覧が取得できること</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.5.5</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -942,7 +973,12 @@
           <t>NodePort/Service外部アクセス確認</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>業務アプリケーションを実際に外部から利用できることを確認する、エンドユーザー視点での受け入れ試験。</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>kubectl expose job/sample-training-job --type=NodePort --port=80 -n ai-training --dry-run=client -o yaml
 # (実運用対象Serviceで)
@@ -950,24 +986,24 @@
 curl http://&lt;外部LB VIP&gt;:&lt;NodePort&gt;</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>期待するレスポンスが返ること</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.5.5</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>確認後、検証用リソースは削除する</t>
         </is>
@@ -994,7 +1030,12 @@
           <t>Control Plane 1台停止試験</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>3台構成の可用性設計（基本設計書4.1.1）が机上の設計だけでなく実際に機能することを、意図的な障害注入によって実証するため。</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t># 対象CPノード上で実行
 sudo systemctl stop kubelet
@@ -1008,24 +1049,24 @@
 sudo systemctl start kubelet</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>停止中もkubectl操作・既存業務Podが継続動作すること。復旧後、対象ノードが自動的にReadyへ復帰すること</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.1.1</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>検証は業務影響が無い時間帯に実施</t>
         </is>
@@ -1045,7 +1086,12 @@
           <t>Worker Node 1台停止試験</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Pod Anti-Affinity等の可用性設計（基本設計書4.1.2/4.1.3）が実際に機能し、業務が継続できることを実証するため。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t># 対象Workerノード上で実行
 sudo systemctl stop kubelet
@@ -1058,24 +1104,24 @@
 sudo systemctl start kubelet</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>正常ノードで業務継続、GPU学習ジョブは縮退運転（順次実行）に切り替わること。復旧後、自動的にReadyへ復帰すること</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.1.2</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>検証は業務影響が無い時間帯に実施</t>
         </is>
@@ -1102,30 +1148,35 @@
           <t>サービス一覧・パッケージ一覧採取</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>構築完了時点の状態を記録として残すことで、以後の変更管理や障害発生時の切り分け（何が変わったか）の基準（ベースライン）とするため。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>systemctl list-unit-files &gt; service-list-$(hostname).txt
 dpkg -l &gt; package-list-$(hostname).txt</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>各ノードでファイルが生成され、内容がパラメータシート「構築後採取一覧」へ転記されていること</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>パラメータシート 構築後採取一覧</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1145,31 +1196,36 @@
           <t>クラスタ情報・Helmリリース一覧採取</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>同上。クラスタの構成管理・監査証跡として、構築完了時点のバージョン・リリース状況を記録するため。</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>kubectl get nodes -o wide &gt; cluster-nodes.txt
 kubectl version &gt; cluster-version.txt
 helm list -A &gt; helm-releases.txt</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>各ファイルが生成され、内容がパラメータシート「構築後採取一覧」へ転記されていること</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>パラメータシート 構築後採取一覧</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1191,44 +1247,49 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
+          <t>実施結果の記録を関係者間で確認・合意することで、後工程（運用引き継ぎ等）へ責任を持って引き継ぐため。</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
           <t>（レビュー・承認作業のためCLIコマンド無し）
 本手順書全項目の実施結果を確認し、関係者による完了確認・承認を行う。</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>本手順書全項目の実施結果が「完了」または合意の上「対象外」であること</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>本手順書 全シート</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>未完了・NG項目が残る場合は課題管理台帳へ転記のうえ引き継ぐ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J16"/>
+  <autoFilter ref="A3:K16"/>
   <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G7 G8 G9 G11 G12 G14 G15 G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H7 H8 H9 H11 H12 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1547,19 +1608,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1587,35 +1649,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -1644,28 +1711,33 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
+          <t>物理的にサーバーを設置しなければ後続のBIOS設定・OSインストールが一切開始できないため。冗長電源2系統への結線は、電源ユニット単体故障時にも継続稼働できる可用性設計（基本設計書ハードウェア設計）を成立させる前提条件となる。</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
           <t>（物理作業のためCLIコマンド無し）
 Control Plane×3（HPE DL360 Gen12）、Worker×2（HPE DL380 Gen12）をラックへ搭載し、冗長電源2系統を結線する。ノード用NIC・iLO用NICを、パラメータシート「ノード構成」記載のスイッチポートへ結線する。</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>両電源ユニットのランプ点灯、スイッチ側のリンクアップランプ点灯を目視確認</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>パラメータシート ノード構成、ハードウェア設定</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>CLIコマンド無し（現地物理作業のため）</t>
         </is>
@@ -1685,7 +1757,12 @@
           <t>iLO(BMC)初期設定・疎通確認</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>OSインストール（仮想メディア経由）、リモート電源操作、障害時のコンソールアクセスはいずれもiLO経由で行うため、OSインストール前にiLOのネットワーク到達性を確保しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t># 管理端末から疎通確認
 ping -c 4 &lt;各ノードのiLO IPアドレス&gt;
@@ -1694,24 +1771,24 @@
 # ログイン後、管理者パスワードを変更する</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>ping応答成功、Web GUIへのログイン成功</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>ハードウェア設定 サーバ管理モジュール</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>変更後のパスワードは本書に記載せず、パスワード管理台帳で管理</t>
         </is>
@@ -1732,6 +1809,11 @@
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>仮想化支援機能（VT-x/VT-d）が無効だとcontainerd/Kubernetesのコンテナ実行基盤が正しく動作しない。UEFIブートモードはOSインストーラの前提であり、電源性能設定はAI学習ワークロードの処理性能に直結するため、OSインストール前に確定させておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>（BIOSメニュー操作のためCLIコマンド無し）
 起動時にF9等でBIOSセットアップへ入り、以下を設定する。
@@ -1740,24 +1822,24 @@
 - Power Profile: Maximum Performance</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>BIOS設定画面で各項目が設定値通りであることを目視確認</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>CLIコマンド無し（BIOSメニュー操作のため）。iLO RESTful API（iLOREST）による自動化も可能（本書では対象外）</t>
         </is>
@@ -1777,31 +1859,36 @@
           <t>RAID構成確認</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Bootドライブのミラーリング（RAID1）、Worker学習データ用SSDのRAID10構成は、ディスク故障時のデータ保護と性能（基本設計書ハードウェア設計）の前提となる。OSインストール後はRAID構成の変更が困難なため、事前に確認する。</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t># HPE Smart Storage Administrator CLI(ssacli)で論理ドライブを確認（Ubuntu起動後に実施）
 sudo apt-get install -y ssacli
 sudo ssacli ctrl slot=0 ld all show detail</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Bootドライブ論理ドライブ=RAID1、Worker用データSSD論理ドライブ=RAID10、いずれもStatus=OKであること</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>パラメータシート ハードウェア設定</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>ssacliパッケージはHPE公式リポジトリから導入</t>
         </is>
@@ -1828,7 +1915,12 @@
           <t>kube-apiserver用VIP設定</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>kubeadmでHA構成のControl Planeを構築するには、全ノード共通のcontrolPlaneEndpoint（VIP）がPhase4のkubeadm init実行前に確定・疎通可能である必要があるため。構築後の変更は極めて困難なため事前確定が必須。</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>（ベンダー製品のGUI/CLI操作のため個別コマンド無し）
 外部ロードバランサ管理画面で以下を設定する。
@@ -1838,25 +1930,25 @@
 - ヘルスチェック: TCP/6443（この時点ではAPIサーバー未構築のため疎通のみ）</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t># 管理端末から経路疎通確認（未構築のため6443でRST/timeoutでも経路上の疎通確認としては可）
 nc -zv &lt;VIP&gt; 6443</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.5.5、パラメータシート ノード構成</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>ベンダー製品固有の設定コマンドは外部LB設計書に準ずる</t>
         </is>
@@ -1876,30 +1968,35 @@
           <t>NodePort公開用VIP設定</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>業務アプリケーションを外部公開する経路を、クラスタ構築完了後すぐに利用できるよう事前に準備しておくため。</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>（ベンダー製品のGUI/CLI操作）
 業務アプリケーション公開用VIPを設定し、バックエンドにWorker×2のNodePortレンジ(30000-32767)を登録する。</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>設定内容のレビュー完了、nc -zv &lt;VIP&gt; &lt;確認用ポート&gt; で経路疎通確認</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.5.5</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>公開対象Serviceが未確定の場合は仮設定とし、Phase8で実サービスに合わせて調整</t>
         </is>
@@ -1919,38 +2016,43 @@
           <t>DNS正引き・逆引き登録</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>kubeadmやノード間通信・運用操作はホスト名を前提とする箇所が多く、IPアドレス管理だけでは運用性・可読性に劣るため、構築前に名前解決を確立しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>（DNS管理コンソール/ゾーンファイル編集のため個別コマンド無し）
 全5ノードのAレコード・PTRレコードを登録する。</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>dig k8s-cp01.&lt;ドメイン名&gt;
 dig -x &lt;k8s-cp01のIPアドレス&gt;
 （他4ノードも同様に確認）</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.5.2</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>DNS製品固有の登録手順（BIND/Windows DNS等）は別途参照</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
@@ -1964,31 +2066,36 @@
           <t>NTPサーバー疎通確認</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>etcdの分散合意やTLS証明書の有効期限検証はノード間の時刻同期を前提とする。時刻がずれた状態でクラスタを構築すると原因究明が困難な障害につながるため、Phase3での恒久設定に先立ち疎通のみ確認しておく。</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t># 確認用に一時導入し疎通確認（恒常設定はPhase3で実施）
 sudo apt-get install -y ntpdate
 ntpdate -q &lt;NTPサーバーのIPアドレス&gt;</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>オフセット値が返り疎通できること</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.5.1</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>恒常的な時刻同期はPhase3のchrony設定で実施</t>
         </is>
@@ -2008,7 +2115,12 @@
           <t>外部リポジトリ疎通確認</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>containerd/kubeadm/Calico/Trident/NVIDIA関連の各種パッケージはすべてインターネット上の公式リポジトリから取得する。Phase3以降の導入作業を疎通不良で止めないよう、事前に確認しておく。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>curl -I https://registry.k8s.io
 curl -I https://pkgs.k8s.io
@@ -2019,24 +2131,24 @@
 curl -I https://nvidia.github.io</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>各URLで200または30x応答が返ること（プロキシ経由の場合は各コマンドへ -x &lt;proxyURL&gt; を付与）</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>疎通不可の場合は社内プロキシ設定をOS設定へ追記</t>
         </is>
@@ -2049,7 +2161,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="40.5" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>10</v>
       </c>
@@ -2065,43 +2177,48 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
+          <t>podSubnet・controlPlaneEndpoint等はkubeadmでのクラスタ構築後は原則変更できない（変更には再構築が必要となる）ため、後戻りできない設計判断はすべてこの時点で確定させておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
           <t>（設計判断作業のためCLIコマンド無し）
 パラメータシート「ノード構成」シートの各ノードIPアドレス、controlPlaneEndpoint、podSubnet等の「※要決定」項目を確定し反映する。</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>パラメータシートの「※要決定」項目がすべて確定値に更新されていること</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>パラメータシート 全シート</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>確定後、後続フェーズの前提となるため関係者レビューを実施</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J16"/>
+  <autoFilter ref="A3:K16"/>
   <mergeCells count="4">
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G10 G11 G12 G13 G14 G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H10 H11 H12 H13 H14 H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2115,19 +2232,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2155,35 +2273,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -2212,28 +2335,33 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
+          <t>OSをインストールするための出発点。パラメータシートで確定したUbuntu 24.04 LTSを、ノードが認識できる形で提供する必要がある。</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
           <t>（物理/iLO仮想メディア操作のためCLIコマンド無し）
 Ubuntu Server 24.04 LTS ISOイメージをiLO仮想メディア機能等で各ノードにマウントする。</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>起動時にインストーラのブートメニューが表示されること</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>CLIコマンド無し（iLO GUI操作のため）</t>
         </is>
@@ -2262,34 +2390,39 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
+          <t>運用上の一貫性（ログ・日時表記の統一）を確保するため、パラメータシートで定めた標準値に全ノードを揃える。</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
           <t>（インストーラGUI/TUI操作のためCLIコマンド無し）
 言語=English、タイムゾーン=Asia/Tokyo、キーボード=Japaneseを選択する。</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>設定画面で選択内容を確認</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>CLIコマンド無し（対話式インストーラのため）</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40.5" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>3</v>
       </c>
@@ -2305,28 +2438,33 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
+          <t>kubeadmやCalico、外部LBとの通信はすべて固定IPを前提として設計されている（controlPlaneEndpoint等がIP/ホスト名で固定参照されるため）ため、DHCPではなく静的IPで導入する必要がある。</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
           <t>（インストーラGUI/TUI操作）
 IPv4手動設定でパラメータシート記載のIPアドレス・ネットマスク・ゲートウェイ・DNSを入力し、ホスト名を設定する。IPv6は無効化する。</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>インストーラのネットワークテスト成功、または再起動後 ip a / hostnamectl で確認</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>パラメータシート ノード構成、OS設定_共通</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>CLIコマンド無し（対話式インストーラのため）</t>
         </is>
@@ -2348,34 +2486,39 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
+          <t>swap領域が存在するとkubeletが起動しない（Kubernetesの既定要件）ため、OSインストールの時点でswapを作らないパーティション構成にしておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
           <t>（インストーラGUI/TUI操作）
 手動構成を選択し、/（ext4）、/boot/efi（EFI System Partition, 600MB）を作成する。swap領域は作成しない。</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>再起動後 lsblk / df -h でパーティション構成を確認</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>swap未作成であることを必ず確認（kubelet起動要件）。CLIコマンド無し（対話式インストーラのため）</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="27" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
@@ -2391,28 +2534,33 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
+          <t>root直接ログインを許可すると操作の追跡性・セキュリティが低下する。以降のすべての作業を一般ユーザー+sudoで実施する前提を、OSインストール時点で作る必要がある。</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
           <t>（インストーラGUI/TUI操作）
 管理ユーザーを作成し、SSH公開鍵を登録する。rootの直接ログインは無効のままとする。</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>管理ユーザーでのSSHログイン成功、rootログインが拒否されること</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>パスワードは本書・パラメータシートに記載せず、パスワード管理台帳で管理。CLIコマンド無し（対話式インストーラのため）</t>
         </is>
@@ -2439,7 +2587,12 @@
           <t>autoinstall用user-data作成</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>5台同一構成のノードを対話式インストーラで手作業導入すると、設定ミスや作業品質のばらつきが生じやすい。構成をコード化（autoinstall）することで、再現性と作業速度を両立できる。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>#cloud-config形式のuser-dataを作成し、USBメディア等に配置する（ノードごとにIP/ホスト名を変更）
 autoinstall:
@@ -2471,24 +2624,24 @@
     - "sed -i '/\\sswap\\s/d' /target/etc/fstab"</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>（本手順を使う場合）自動インストール完了後、Phase2最終確認へ進む</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>swapを作らないlate-commandsを明示している点がKubernetes向けの固有設定。手動インストールを行う場合は本行は対象外とする</t>
         </is>
@@ -2515,7 +2668,12 @@
           <t>初回起動・疎通確認</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>以降の作業はすべてSSH経由のリモート操作となるため、疎通と設計値通りの状態（パーティション・ホスト名等）を次工程に進む前に確認しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t># 管理端末から実行
 ssh &lt;管理ユーザー&gt;@&lt;ノードのIPアドレス&gt;
@@ -2526,40 +2684,40 @@
 uname -a</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>SSHログイン成功、IPアドレス・ホスト名・パーティション構成が設計値通りであること、free -h でSwap行が0であること</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>パラメータシート ノード構成、OS設定_共通</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J14"/>
+  <autoFilter ref="A3:K14"/>
   <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G7 G8 G9 G10 G12 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H7 H8 H9 H10 H12 H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2573,19 +2731,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2613,35 +2772,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -2668,36 +2832,41 @@
           <t>OSパッケージ更新</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>既知の脆弱性や不具合を含んだ状態のままKubernetes基盤を構築しないため、導入作業に先立ちOSを最新化する。</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>sudo apt-get update
 sudo apt-get upgrade -y</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>エラーなく完了すること</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27" customHeight="1">
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
@@ -2711,30 +2880,35 @@
           <t>ファイアーウォール(ufw)無効化</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>CNI（Calico）はPod間通信制御のためiptables/nftablesルールを自ら動的に書き換える。ufwが同時に稼働していると双方のルールが競合し、Pod通信が意図せず遮断される場合があるため無効化する。</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>sudo systemctl disable --now ufw
 sudo ufw status</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>"Status: inactive" と表示されること</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>Kubernetes/CNIが管理するiptablesとの競合回避のため</t>
         </is>
@@ -2754,7 +2928,12 @@
           <t>chrony設定</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Phase1で疎通確認したNTPサーバーへの同期を恒久化する。etcdの分散合意・TLS証明書の有効性検証はノード間の時刻同期が前提となるため必須の設定となる。</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>sudo apt-get install -y chrony
 sudo tee -a /etc/chrony/chrony.conf &gt; /dev/null &lt;&lt;EOF
@@ -2765,25 +2944,25 @@
 sudo systemctl restart chrony</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>chronyc sources で同期先が表示されること
 chronyc tracking で Leap status: Normal であること</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2803,7 +2982,12 @@
           <t>unattended-upgrades設定</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>セキュリティパッチは自動適用しつつ、自動再起動によってクラスタが意図せずダウンすることを防ぐため、再起動は無効化しメンテナンス時に手動で行う運用とする。</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>sudo apt-get install -y unattended-upgrades
 sudo tee /etc/apt/apt.conf.d/50unattended-upgrades &gt; /dev/null &lt;&lt;EOF
@@ -2815,24 +2999,24 @@
 sudo systemctl enable --now unattended-upgrades</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>sudo unattended-upgrade --dry-run --debug でsecurity対象のみ検出されること</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>Kubernetes関連パッケージはapt-mark holdで別途固定するため対象外となる</t>
         </is>
@@ -2859,31 +3043,36 @@
           <t>swap無効化</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>kubeletはswapが有効なノードでは起動しない（Kubernetesの既定要件）。パーティション設計に加え、既存インストールに対しても明示的に無効化しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>sudo swapoff -a
 sudo sed -i.bak '/\sswap\s/s/^/#/' /etc/fstab
 free -h</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>free -h の Swap 行が 0 であること。再起動後も無効のままであること</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>kubelet起動要件</t>
         </is>
@@ -2903,7 +3092,12 @@
           <t>カーネルモジュール設定</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>overlayはcontainerdが使用するオーバーレイファイルシステムに、br_netfilterはブリッジ経由のパケットをiptablesで制御するために、それぞれ必須となるカーネル機能。無いとPod間通信が正しく行えない。</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF | sudo tee /etc/modules-load.d/k8s.conf
 overlay
@@ -2913,24 +3107,24 @@
 sudo modprobe br_netfilter</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>lsmod | grep -e overlay -e br_netfilter でいずれもロード済みであること</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2950,7 +3144,12 @@
           <t>sysctl設定</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>net.ipv4.ip_forwardを有効にしないとノードがルーターとして機能せず、Podネットワークのパケット転送ができない。bridge-nf-call-iptablesは、CNIが設定するiptablesルールをブリッジ経由の通信にも適用させるための必須設定。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF | sudo tee /etc/sysctl.d/k8s.conf
 net.bridge.bridge-nf-call-iptables  = 1
@@ -2960,24 +3159,24 @@
 sudo sysctl --system</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>sysctl net.ipv4.ip_forward 等、各パラメータが設定値通りであること</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>Pod間通信・転送の前提設定</t>
         </is>
@@ -3004,7 +3203,12 @@
           <t>containerdインストール</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>kubeletが唯一操作するCRI（Container Runtime Interface）実装として、パラメータシートで採用を決めたコンテナランタイムを導入する。これが無いとPodを一つも起動できない。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t># Docker公式aptリポジトリからcontainerd.ioパッケージを導入（Ubuntu 24.04標準リポジトリより新しいバージョンを利用するため）
 sudo install -m 0755 -d /etc/apt/keyrings
@@ -3016,24 +3220,24 @@
 ctr version</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>ctr version の出力バージョンが2.3系であること</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3053,7 +3257,12 @@
           <t>containerd設定反映</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>kubeletの既定cgroupドライバ（systemd）とcontainerd側の設定が一致していないと、リソース管理が二重管理状態となりノードが不安定化する既知の問題があるため統一する。pause imageの明示固定は、kubeadmが期待するバージョンとの不整合による警告・非互換を防ぐため。</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>sudo mkdir -p /etc/containerd
 containerd config default | sudo tee /etc/containerd/config.toml &gt; /dev/null
@@ -3063,25 +3272,25 @@
 sudo systemctl enable containerd</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>grep SystemdCgroup /etc/containerd/config.toml → true であること
 systemctl status containerd がactiveであること</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 containerd設定</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>SystemdCgroup=trueはkubelet(systemdドライバ)との整合に必須</t>
         </is>
@@ -3108,7 +3317,12 @@
           <t>Kubernetes aptリポジトリ登録・パッケージ導入</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>クラスタを構築・操作するための本体コンポーネント（kubeadm/kubelet/kubectl）を導入する。apt-mark holdでバージョンを固定するのは、自動更新によりノード間でバージョンがばらつき、互換性問題が生じるのを防ぐため。</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>sudo apt-get install -y apt-transport-https ca-certificates curl gpg
 sudo mkdir -p /etc/apt/keyrings
@@ -3120,25 +3334,25 @@
 kubeadm version</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>kubeadm version / kubelet --version / kubectl version --client でv1.35系が表示されること
 apt-mark showhold で3パッケージが固定されていること</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定、OS設定_共通</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>v1.35リポジトリ内の最新パッチが自動選択される（構築時点でv1.32はEOLのため使用しない）</t>
         </is>
@@ -3158,7 +3372,12 @@
           <t>Helmインストール</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>監視スタック(kube-prometheus-stack)やTrident等、本設計で採用するソフトウェアの多くがHelm Chartとして配布されているため、Control Plane上での作業実行に必要となる。</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>curl -fsSL -o helm.tar.gz https://get.helm.sh/helm-v4.2.3-linux-amd64.tar.gz
 tar -zxvf helm.tar.gz
@@ -3167,24 +3386,24 @@
 helm version</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>helm version の出力が v4.2.3 系であること</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>パラメータシート OS設定_共通</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>既存Chart/CIがv3系前提の場合は互換性を事前確認。実施時点の最新版は https://github.com/helm/helm/releases で要確認</t>
         </is>
@@ -3211,7 +3430,12 @@
           <t>NVIDIA Driverインストール</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>GPUをOSが認識するための基盤ドライバ。これが無いとcontainerd/Kubernetes以前に、OSレベルでGPUデバイス自体を利用できない。</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>sudo apt-get install -y ubuntu-drivers-common
 sudo ubuntu-drivers install --gpgpu
@@ -3220,24 +3444,24 @@
 nvidia-smi</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>nvidia-smi でH100 NVLが認識され、ドライババージョンが表示されること</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.8、パラメータシート Kubernetes設定</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3257,7 +3481,12 @@
           <t>NVIDIA Container Toolkitインストール</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Driverだけではコンテナ（Pod）内からGPUデバイスにアクセスできない。containerdのランタイムをGPU対応に拡張し、Pod内にGPUデバイスを渡せるようにするために必須となる。</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>curl -fsSL https://nvidia.github.io/libnvidia-container/gpgkey | sudo gpg --dearmor -o /usr/share/keyrings/nvidia-container-toolkit-keyring.gpg
 curl -s -L https://nvidia.github.io/libnvidia-container/stable/deb/nvidia-container-toolkit.list | sed 's#deb https://#deb [signed-by=/usr/share/keyrings/nvidia-container-toolkit-keyring.gpg] https://#g' | sudo tee /etc/apt/sources.list.d/nvidia-container-toolkit.list
@@ -3267,30 +3496,30 @@
 sudo systemctl restart containerd</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>nvidia-ctk --version でバージョン確認、grep nvidia /etc/containerd/config.toml でruntime設定が反映されていること</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.8、パラメータシート Kubernetes設定</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="27" customHeight="1">
+    <row r="22" ht="40.5" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>14</v>
       </c>
@@ -3304,29 +3533,34 @@
           <t>nfs-commonインストール</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>NetApp Trident（NFSバックエンド）はOS側のNFSクライアント機能を利用してボリュームをマウントするため、事前導入が無いとPersistentVolumeのマウントに失敗する。</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>sudo apt-get install -y nfs-common</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>dpkg -l | grep nfs-common で導入確認</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 CSI設定</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>NetApp Trident（NFSバックエンド）利用の前提</t>
         </is>
@@ -3353,7 +3587,12 @@
           <t>再起動・状態確認</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>sysctl・カーネルモジュール・swap設定がファイルとして永続化されているかを確認しないと、後日の再起動で設定が失われクラスタが不安定化するリスクがある。構築初期のうちに再起動耐性を確認しておく。</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>sudo reboot
 # 再起動後
@@ -3362,42 +3601,42 @@
 systemctl status kubelet</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Swap=0、containerdがactive、kubeletはクラスタ未参加のためactivating(auto-restart)で正常であること</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr"/>
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J24"/>
+  <autoFilter ref="A3:K24"/>
   <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G10 G11 G12 G14 G15 G17 G18 G20 G21 G22 G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H10 H11 H12 H14 H15 H17 H18 H20 H21 H22 H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3411,19 +3650,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3451,35 +3691,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -3506,7 +3751,12 @@
           <t>kubeadm-config.yaml作成</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>対話式コマンドオプションの手打ちではなく設定ファイルとして明示することで、3台のControl Plane・パラメータシートの値と食い違いなく再現性を持ってクラスタを構築するため。</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t># kubeadm versionでインストール済みバージョンを確認
 kubeadm version -o short
@@ -3536,24 +3786,24 @@
 EOF</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>ファイル内容がパラメータシート「Kubernetes設定 kubeadm ClusterConfiguration」の値と一致していること</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 kubeadm ClusterConfiguration</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>apiVersion(v1beta4)は本書作成時点の最新。実施時に異なる場合は kubeadm config migrate で変換可能</t>
         </is>
@@ -3573,29 +3823,34 @@
           <t>kubeadm init実行</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>1台目のControl Planeを初期化し、etcd・kube-apiserver等クラスタの中枢コンポーネントを立ち上げる、クラスタ構築全体の起点となる作業。</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>sudo kubeadm init --config kubeadm-config.yaml --upload-certs | tee kubeadm-init.log</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>"Your Kubernetes control-plane has initialized successfully" が出力され、Control Plane用joinコマンド・Worker用joinコマンドが出力されること</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>出力されたjoinコマンド・certificate-keyをkubeadm-init.logごと安全に保管する（certificate-keyの既定有効期限は2時間）</t>
         </is>
@@ -3615,7 +3870,12 @@
           <t>kubectl設定</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>kubeadmが生成した管理者用認証情報（admin.conf）をkubectlの参照先に配置しないと、以降のkubectlコマンドが一切実行できないため。</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>mkdir -p $HOME/.kube
 sudo cp -i /etc/kubernetes/admin.conf $HOME/.kube/config
@@ -3623,24 +3883,24 @@
 kubectl get nodes</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>kubectl get nodes が実行でき、k8s-cp01のみSTATUS=NotReadyで表示されること（CNI未導入のため正常）</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3667,7 +3927,12 @@
           <t>Control Plane追加join</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>基本設計書の可用性設計（Control Plane 3台構成）を満たすため、1台のControl Planeだけで終わらせず、残り2台を追加してetcd・kube-apiserverを冗長化する。</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t># kubeadm-init.logに出力された、以下形式のControl Plane用joinコマンドを実行する
 sudo kubeadm join &lt;VIP&gt;:6443 --token &lt;token&gt; \
@@ -3678,24 +3943,24 @@
 sudo chown $(id -u):$(id -g) $HOME/.kube/config</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>各ノードで "This node has joined the cluster" 相当のメッセージが出力されること</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>token(既定24時間)・certificate-key(既定2時間)が期限切れの場合は次行の再発行コマンドを使用</t>
         </is>
@@ -3715,36 +3980,41 @@
           <t>(期限切れ時のみ)token/certificate-key再発行</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>joinに使うtoken/certificate-keyにはセキュリティ上短い有効期限が設定されているため、作業の間隔が空くと再取得が必要になる。</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>sudo kubeadm init phase upload-certs --upload-certs
 sudo kubeadm token create --print-join-command</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>新しいtoken/certificate-keyが出力されること</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>期限切れが無ければ本行はスキップ</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40.5" customHeight="1">
+    <row r="11" ht="27" customHeight="1">
       <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
@@ -3758,29 +4028,34 @@
           <t>Control Plane 3台の参加確認</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>3台のControl Planeが正しくクラスタに認識されていることを、次工程（CNI導入）に進む前に確認するため。</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>kubectl get nodes</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>cp01, cp02, cp03の3ノードが表示されること（CNI未導入のため全てNotReady）</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.1.1</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3807,31 +4082,36 @@
           <t>Calico CRD・Tigera Operatorインストール</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>kubeadmはPodネットワーク（CNI）を自動導入しない。ノードがNotReadyのままなのはCNI未導入のためであり、Podを一つも起動できるようにするには別途CNIプラグインの導入が必須となる。</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>kubectl create -f https://raw.githubusercontent.com/projectcalico/calico/v3.32.1/manifests/v1_crd_projectcalico_org.yaml
 kubectl create -f https://raw.githubusercontent.com/projectcalico/calico/v3.32.1/manifests/tigera-operator.yaml
 kubectl get pods -n tigera-operator</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>tigera-operator NamespaceのPodがRunningになること</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 CNI設定</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>サイズが大きいためkubectl applyではなくkubectl createを使用する（公式手順）</t>
         </is>
@@ -3851,7 +4131,12 @@
           <t>Calico custom-resources適用</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>実際のPodネットワーク（IPPool/カプセル化方式）のパラメータをCalicoへ反映する工程。ここでpodSubnetと一致させないと、Podに正しくIPアドレスが割り当たらない。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF &gt; custom-resources.yaml
 apiVersion: operator.tigera.io/v1
@@ -3876,30 +4161,30 @@
 kubectl create -f custom-resources.yaml</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>kubectl get pods -n calico-system で全PodがRunningになること（数分要する）</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 CNI設定</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>カプセル化方式(encapsulation)は入門コースでの確認結果を反映</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>9</v>
       </c>
@@ -3913,29 +4198,34 @@
           <t>Control Plane Ready確認</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>CNI導入によりノードがNotReadyからReadyへ遷移することを確認し、次のWorker参加工程に進めることを保証するため。</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>kubectl get nodes</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>cp01, cp02, cp03の3ノードすべてがSTATUS=Readyであること</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3962,31 +4252,36 @@
           <t>Worker join実行</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>実際に業務Pod・GPU学習ジョブを稼働させるWorker Nodeをクラスタに参加させる、基本設計の中核となる作業。</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t># kubeadm-init.logに出力された、以下形式のWorker用joinコマンドを実行する
 sudo kubeadm join &lt;VIP&gt;:6443 --token &lt;token&gt; \
   --discovery-token-ca-cert-hash sha256:&lt;hash&gt;</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>各ノードで "This node has joined the cluster" が出力されること</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>tokenが期限切れの場合はcp01で kubeadm token create --print-join-command</t>
         </is>
@@ -4006,29 +4301,34 @@
           <t>全ノードReady確認</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>5ノード構成が設計通り完成したことを確認する、クラスタ構築フェーズの完了マイルストーンとなる。</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>kubectl get nodes -o wide</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>全5ノードがSTATUS=Readyであること</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4048,37 +4348,42 @@
           <t>Control Plane taint確認</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>基本設計書の方針（業務PodはWorker Nodeのみに配置し、Control Planeには配置しない）が実際に機能する前提となるtaintが、kubeadmにより自動付与されているかを確認するため。</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>kubectl describe node k8s-cp01 | grep -A3 Taints
 kubectl describe node k8s-cp02 | grep -A3 Taints
 kubectl describe node k8s-cp03 | grep -A3 Taints</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>各CPノードに node-role.kubernetes.io/control-plane:NoSchedule のtaintが表示されること（kubeadmにより自動付与）</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 Pod配置・リソース管理</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="27" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="11" t="n">
         <v>13</v>
       </c>
@@ -4092,45 +4397,50 @@
           <t>クラスタ証明書有効期限確認</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>kubeadmが生成する内部証明書は既定で有効期限（通常1年）があり、期限切れするとAPIサーバーにアクセスできなくなる重大障害となる。構築直後の期限を記録し、以後の証明書監視（基本設計書4.4.2）の基準値とする。</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>sudo kubeadm certs check-expiration</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>コマンドが正常実行され、各証明書の有効期限一覧が出力されること</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.4.2</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>証明書監視の初期値として記録</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J20"/>
+  <autoFilter ref="A3:K20"/>
   <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G9 G10 G11 G13 G14 G15 G17 G18 G19 G20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H9 H10 H11 H13 H14 H15 H17 H18 H19 H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4144,19 +4454,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4184,35 +4495,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -4225,7 +4541,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="27" customHeight="1">
+    <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
@@ -4241,28 +4557,33 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
+          <t>Tridentが実ストレージ側に接続するための情報（管理LIF/SVM/アグリゲート等）が確定していないと、後続のTridentBackendConfig作成が行えないため。</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
           <t>（外部ストレージ管理者との調整作業のためCLIコマンド無し）
 管理LIF疎通、利用予定SVM・アグリゲート・プロトコル(NFS)の準備状況を確認する。</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>ping &lt;ONTAP管理LIFのIPアドレス&gt; で疎通確認。SVM/アグリゲートの空き容量確認</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.7.2（※接続情報は未パラメータ化のため本行で確定）</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>TridentBackendConfig作成に必要な値をここで確定する</t>
         </is>
@@ -4282,7 +4603,12 @@
           <t>Trident Operatorインストール</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>KubernetesからNetAppストレージを操作するためのCSIドライバ（Trident）本体を導入する。これが無いとPersistentVolumeの動的プロビジョニングができない。</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>kubectl create namespace trident
 helm repo add netapp-trident https://netapp.github.io/trident-helm-chart
@@ -4291,24 +4617,24 @@
 kubectl get pods -n trident</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>trident Namespace配下のPod(trident-operator, trident-controller等)がRunningになること</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 CSI設定</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>Helm Chartバージョン100.2606.0がTrident 26.06に対応（実施時は要最新確認）</t>
         </is>
@@ -4328,7 +4654,12 @@
           <t>ONTAP接続用Secret作成</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>認証情報をYAMLに平文で埋め込むとGit管理等で漏えいリスクが生じるため、Kubernetes Secretとして分離管理し、TridentBackendConfigからは参照のみとすることで露出を防ぐ。</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>kubectl create secret generic backend-tbc-ontap-nas-secret \
   --from-literal=username=&lt;ONTAP接続ユーザー名&gt; \
@@ -4336,24 +4667,24 @@
   -n trident</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>kubectl get secret -n trident でSecretが作成されていること</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>認証情報は本書・パラメータシートに記載せず、パスワード管理台帳で管理</t>
         </is>
@@ -4373,7 +4704,12 @@
           <t>TridentBackendConfig作成</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Kubernetesに「どの物理ストレージへ、どういう手段で接続するか」を教える設定。これが無いと、StorageClass経由のPVC要求に応じてボリュームを払い出すことができない。</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF &gt; backend-ontap-nas.yaml
 apiVersion: trident.netapp.io/v1
@@ -4393,24 +4729,24 @@
 kubectl apply -f backend-ontap-nas.yaml</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>kubectl get tridentbackendconfig -n trident で Phase=Bound であること</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.7.2</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4430,7 +4766,12 @@
           <t>StorageClass作成</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>利用者がPVCで「どんな特性のストレージが欲しいか」を指定するためのテンプレート。デフォルト指定することでPVCにstorageClassNameを省略しても、このストレージが自動的に使われるようにするため。</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF &gt; storageclass-netapp-nas.yaml
 apiVersion: storage.k8s.io/v1
@@ -4450,24 +4791,24 @@
 kubectl apply -f storageclass-netapp-nas.yaml</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>kubectl get storageclass で netapp-nas が (default) 付きで表示されること</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 CSI設定</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4487,7 +4828,12 @@
           <t>PVC/Pod動作確認</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>設定が机上で正しくても、実際にボリュームの作成・マウント・書き込みが動作するとは限らない。監視スタックやAI学習ジョブの本番投入前に、実データでの疎通を確認しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF &gt; test-pvc-pod.yaml
 apiVersion: v1
@@ -4524,24 +4870,24 @@
 kubectl delete -f test-pvc-pod.yaml</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>"hello" が出力されること（PV経由での書き込み・読み込み成功）</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>確認後、検証用リソースは削除する</t>
         </is>
@@ -4568,7 +4914,12 @@
           <t>NVIDIA Device Pluginデプロイ</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>kubeletは標準ではGPUをリソースとして認識しない。Device Pluginを介して初めて、Podのrequests/limitsにnvidia.com/gpuを指定できるようになるため。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>helm repo add nvdp https://nvidia.github.io/k8s-device-plugin
 helm repo update
@@ -4576,24 +4927,24 @@
   --namespace nvidia-device-plugin --create-namespace --version 0.17.1</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>kubectl get pods -n nvidia-device-plugin でRunningを確認</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 GPU設定</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>GPU Operator採用の場合は代替手順とする（本手順はDevice Plugin単体導入）</t>
         </is>
@@ -4613,30 +4964,35 @@
           <t>GPUノードtaint付与</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>GPUを使わない一般業務PodがGPU搭載ノードに誤って配置され、貴重なGPUノードのリソースを占有してしまうのを防ぐため（基本設計書3.6 Pod配置方針）。</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>kubectl taint nodes k8s-wk01 nvidia.com/gpu=present:NoSchedule
 kubectl taint nodes k8s-wk02 nvidia.com/gpu=present:NoSchedule</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>kubectl describe node k8s-wk01 | grep Taints で反映を確認</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 GPU設定、Pod配置・リソース管理</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4656,7 +5012,12 @@
           <t>GPU認識・動作確認</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Device Plugin導入・taint設定が机上の設定で終わらず、実際にPodからGPUを利用できる状態になっているかを、本番のAI学習ジョブ投入前に確認しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>kubectl describe node k8s-wk01 | grep -A5 Capacity
 cat &lt;&lt;EOF &gt; gpu-test.yaml
@@ -4685,38 +5046,38 @@
 kubectl delete -f gpu-test.yaml</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Capacity欄に nvidia.com/gpu: 1 が表示され、Pod実行ログにH100 NVLの情報が出力されること</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.8</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>確認後、検証用リソースは削除する</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J14"/>
+  <autoFilter ref="A3:K14"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G12 G13 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4730,19 +5091,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4770,35 +5132,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -4825,31 +5192,36 @@
           <t>Namespace作成</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>監視・AI学習・分析の各ワークロードを論理的に分離し、後続のRBAC権限やNetworkPolicy等の適用単位とするため（基本設計書3.6）。</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>kubectl create namespace monitoring
 kubectl create namespace ai-training
 kubectl create namespace analytics</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>kubectl get namespaces で3つとも表示されること</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 Namespace設計</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4876,29 +5248,34 @@
           <t>Kubernetes管理者権限設定</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>cluster-admin相当の強い権限を持つ操作者を明確に限定することで、無制限権限の濫用・誤操作がクラスタ全体へ影響するリスクを防ぐ（最小権限の原則）。</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>kubectl create clusterrolebinding k8s-admins --clusterrole=cluster-admin --user=&lt;管理者ユーザー&gt;</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>kubectl auth can-i "*" "*" --as=&lt;管理者ユーザー&gt; が yes となること</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 RBAC設定</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>cluster-admin付与はKubernetes管理者のみに限定</t>
         </is>
@@ -4918,7 +5295,12 @@
           <t>運用担当者/アプリ利用者権限設定</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>利用者ごとに必要最小限の権限のみを付与することで、意図しないリソース変更・削除を防ぐため（基本設計書3.9.1）。</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t># Namespace単位で組み込みClusterRole(admin/view)をRoleBindingとして割り当てる
 kubectl create rolebinding ai-training-admin --clusterrole=admin --user=&lt;運用担当者&gt; -n ai-training
@@ -4927,24 +5309,24 @@
 kubectl create rolebinding analytics-viewer --clusterrole=view --user=&lt;アプリ利用者&gt; -n analytics</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>kubectl auth can-i &lt;操作&gt; --as=&lt;対象ユーザー&gt; -n &lt;namespace&gt; で想定通りの結果になること</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>基本設計書3.9.1</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4964,31 +5346,36 @@
           <t>監視用ServiceAccount作成</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Prometheus等の監視コンポーネントはメトリクス取得のためKubernetes APIを参照するが、参照以上の権限を与える必要はないため、閲覧専用のServiceAccountとして権限を分離する。</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>kubectl create serviceaccount monitoring-viewer -n monitoring
 kubectl create clusterrolebinding monitoring-viewer-binding \
   --clusterrole=view --serviceaccount=monitoring:monitoring-viewer</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>kubectl auth can-i get pods --as=system:serviceaccount:monitoring:monitoring-viewer -A が yes であること</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 RBAC設定</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5015,7 +5402,12 @@
           <t>values-monitoring.yaml作成</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>監視データの保存期間・保存先・通知先はChartのデフォルト値のままでは本設計の要件（基本設計書4.4）を満たさないため、明示的に上書きする値をファイルとして用意する。</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF &gt; values-monitoring.yaml
 prometheus:
@@ -5042,24 +5434,24 @@
 EOF</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>ファイル内容がパラメータシート「Kubernetes設定 監視設定」の値と一致していること</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 監視設定</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5079,7 +5471,12 @@
           <t>kube-prometheus-stackインストール</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>基本設計書4.4で採用を決めた監視基盤（Prometheus/Alertmanager/Grafana等）を、実際にクラスタへ展開する工程。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>helm repo add prometheus-community https://prometheus-community.github.io/helm-charts
 helm repo update
@@ -5088,24 +5485,24 @@
 kubectl get pods -n monitoring</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>monitoring Namespace配下の全Pod(Prometheus/Alertmanager/Grafana/各Exporter)がRunningになること</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.4.1</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5125,7 +5522,12 @@
           <t>DCGM Exporter導入（GPUメトリクス）</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>標準のkube-prometheus-stackにはGPU固有のメトリクス（使用率・温度等）を収集する仕組みが含まれていないため、別途NVIDIA製Exporterを追加する必要がある。</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>helm repo add gpu-helm-charts https://nvidia.github.io/gpu-monitoring-tools/helm-charts
 helm repo update
@@ -5137,24 +5539,24 @@
   --set tolerations[0].effect=NoSchedule</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>kubectl get pods -n monitoring -l app.kubernetes.io/name=dcgm-exporter でGPU搭載Worker上にのみPodがRunningであること</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>パラメータシート Kubernetes設定 監視設定</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5174,31 +5576,36 @@
           <t>Grafanaダッシュボード疎通確認</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>監視基盤が導入されただけでなく、実際に可視化・障害検知に使える状態であることを、運用開始前に確認するため。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>kubectl get secret monitoring-grafana -n monitoring -o jsonpath="{.data.admin-password}" | base64 -d; echo
 kubectl port-forward -n monitoring svc/monitoring-grafana 3000:80
 # ブラウザで http://localhost:3000 へアクセスし、上記adminパスワードでログイン</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>ログイン成功、Kubernetes標準ダッシュボードでノード/Podメトリクスが表示されること</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.4.1</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>初期パスワードはログイン後に変更し、パスワード管理台帳で管理</t>
         </is>
@@ -5218,45 +5625,50 @@
           <t>Alertmanagerテスト通知確認</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>アラートルールが定義されていても、通知経路（メール等）の設定が誤っていると障害発生時に気づけない。実際に通知が届くことを事前に検証しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>kubectl port-forward -n monitoring svc/monitoring-kube-prometheus-alertmanager 9093:9093 &amp;
 curl -H "Content-Type: application/json" -d '[{"labels":{"alertname":"TestAlert","severity":"critical"}}]' http://localhost:9093/api/v2/alerts</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>設定した通知先へテスト通知メールが届くこと</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.4.3</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>確認後、テスト用アラートは自動的にresolvedとなり通知される</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J15"/>
+  <autoFilter ref="A3:K15"/>
   <mergeCells count="4">
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A10:K10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G7 G8 G9 G11 G12 G13 G14 G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H7 H8 H9 H11 H12 H13 H14 H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5270,19 +5682,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5310,35 +5723,40 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
+          <t>目的・解説（なぜこの作業が必要か）</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
           <t>作業内容（手順・コマンド）</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>確認方法・合格基準</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>参照（基本設計書/パラメータシート）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>実施結果</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -5365,7 +5783,12 @@
           <t>etcdスナップショット取得スクリプト作成</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>etcdにはクラスタの全リソース定義が格納されており、これが失われるとクラスタが復旧不能になる。定期バックアップの実体となるスクリプトを用意する（基本設計書4.2.1）。</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>sudo mkdir -p /var/backups/etcd
 cat &lt;&lt;EOF | sudo tee /usr/local/bin/etcd-snapshot.sh
@@ -5381,24 +5804,24 @@
 sudo chmod +x /usr/local/bin/etcd-snapshot.sh</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>ファイルが作成され実行権限が付与されていること</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.2.1</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>保管世代数(7日)は運用ルールに応じて調整</t>
         </is>
@@ -5418,7 +5841,12 @@
           <t>systemdタイマー設定（毎日00:00実行）</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>手動でのバックアップ取得は取得漏れのリスクがあるため、毎日00:00に自動実行させることで確実性を担保する。</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>cat &lt;&lt;EOF | sudo tee /etc/systemd/system/etcd-snapshot.service
 [Unit]
@@ -5440,24 +5868,24 @@
 sudo systemctl enable --now etcd-snapshot.timer</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>systemctl list-timers | grep etcd-snapshot でタイマーが登録され次回実行時刻が表示されること</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.2.1</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5477,31 +5905,36 @@
           <t>スナップショット初回取得確認</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>スクリプト自体に不備があると、いざ障害が起きた際に初めてバックアップが取れていなかったことが判明する事態になるため、導入直後に正常性を確認しておく必要がある。</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>sudo /usr/local/bin/etcd-snapshot.sh
 ls -la /var/backups/etcd/
 sudo ETCDCTL_API=3 etcdutl snapshot status /var/backups/etcd/snapshot-*.db -w table</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>スナップショットファイルが生成され、snapshot statusでhash/revision等が正常表示されること</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.2.1</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5521,7 +5954,12 @@
           <t>リストア手順の検証</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>バックアップが取得できていても、リストア手順自体に不備があると障害発生時に復旧できない。平常時に一度リストアを試すことで、手順そのものの実効性を担保する（基本設計書4.2.2）。</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t># 検証用に別ディレクトリへリストア（本番データには影響しない）
 sudo ETCDCTL_API=3 etcdutl snapshot restore /var/backups/etcd/snapshot-&lt;日付&gt;.db \
@@ -5529,24 +5967,24 @@
 ls /var/lib/etcd-restore-test</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>エラー無くリストアが完了し、データディレクトリが生成されること</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.2.2</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>本番環境への切替(mv /var/lib/etcd 等)はクラスタ全損時のみ実施する非常時手順のため、平常時は検証のみ実施</t>
         </is>
@@ -5559,7 +5997,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
@@ -5575,42 +6013,47 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
+          <t>etcdバックアップはクラスタの構成情報のみを対象とし、OS自体の障害（ディスク故障等）からの復旧はカバーしない。OS層のバックアップを別途取得することで、あらゆる障害パターンに対応できるようにするため。</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
           <t>（バックアップ製品固有のGUI/CLI操作のため個別コマンド無し）
 外部バックアップソフトウェアによる毎日00:00の定期バックアップジョブを全ノードへ設定する。</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>初回バックアップジョブが正常終了すること（バックアップ管理コンソールで確認）</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>基本設計書4.2.1</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>未実施</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
       <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>バックアップ製品名・具体的な設定コマンドは製品確定後に本行を更新</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,実施中,完了,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>
